--- a/results/exp01-svhn-vgg11-e8-random/20260921-212357/rounds.xlsx
+++ b/results/exp01-svhn-vgg11-e8-random/20260921-212357/rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2278,6 +2278,6563 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:54:50</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6497513267457868</v>
+      </c>
+      <c r="F23" t="n">
+        <v>76.0679164105716</v>
+      </c>
+      <c r="G23" t="n">
+        <v>90.81515058389674</v>
+      </c>
+      <c r="H23" t="n">
+        <v>13</v>
+      </c>
+      <c r="I23" t="n">
+        <v>82.4633</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1:22.46</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>79.4213</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.1717</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.8693</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1852.6945</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>30:52.69</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>7,9,1,6,5,2,0,4,3,8</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>7:16;9:33;1:10;6:61;5:17;2:66;0:67;4:36;3:56;8:33</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>7:[1];9:[1,3,4];1:[1];6:[0,1,2,3,4,7];5:[0];2:[0,1,3,4,6,7];0:[0,2,3,4,6,7];4:[2,4,7];3:[1,3,4,5,7];8:[0,2,5]</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>c7:bw=16,experts=[1]; c9:bw=33,experts=[1,3,4]; c1:bw=10,experts=[1]; c6:bw=61,experts=[0,1,2,3,4,7]; c5:bw=17,experts=[0]; c2:bw=66,experts=[0,1,3,4,6,7]; c0:bw=67,experts=[0,2,3,4,6,7]; c4:bw=36,experts=[2,4,7]; c3:bw=56,experts=[1,3,4,5,7]; c8:bw=33,experts=[0,2,5]</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>16.1442,3.5742,15.0801,12.0068,3.2477,10.0559,5.3326,9.0783,1.6184,3.2831</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:56:10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6457168882066057</v>
+      </c>
+      <c r="F24" t="n">
+        <v>90.51551936078673</v>
+      </c>
+      <c r="G24" t="n">
+        <v>90.81515058389674</v>
+      </c>
+      <c r="H24" t="n">
+        <v>13</v>
+      </c>
+      <c r="I24" t="n">
+        <v>80.3522</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1:20.35</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>77.0724</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.1084</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1933.0687</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>32:13.07</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5,7,4,6,9,8,3,1,2,0</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>5:52;7:15;4:56;6:10;9:50;8:35;3:15;1:62;2:32;0:11</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>5:[0,3,5,6,7];7:[1];4:[0,1,5,6,7];6:[1];9:[0,1,2,4,7];8:[1,4,7];3:[0];1:[0,2,4,5,6,7];2:[2,5,6];0:[3]</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>c5:bw=52,experts=[0,3,5,6,7]; c7:bw=15,experts=[1]; c4:bw=56,experts=[0,1,5,6,7]; c6:bw=10,experts=[1]; c9:bw=50,experts=[0,1,2,4,7]; c8:bw=35,experts=[1,4,7]; c3:bw=15,experts=[0]; c1:bw=62,experts=[0,2,4,5,6,7]; c2:bw=32,experts=[2,5,6]; c0:bw=11,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2.8582,16.2244,9.3270,11.5594,3.9048,3.2380,1.5853,13.5140,9.8192,5.0420</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:57:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6380327048751471</v>
+      </c>
+      <c r="F25" t="n">
+        <v>84.92240319606638</v>
+      </c>
+      <c r="G25" t="n">
+        <v>90.81515058389674</v>
+      </c>
+      <c r="H25" t="n">
+        <v>13</v>
+      </c>
+      <c r="I25" t="n">
+        <v>79.3857</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1:19.39</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>75.929</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1651</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.2907</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2012.6837</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>33:32.68</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>6,4,7,9,2,1,5,8,3,0</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>6:30;4:12;7:10;9:50;2:43;1:10;5:25;8:18;3:10;0:31</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>6:[0,4,6];4:[5];7:[5];9:[0,1,2,4,5];2:[0,5,6,7];1:[0];5:[1,5];8:[0];3:[5];0:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>c6:bw=30,experts=[0,4,6]; c4:bw=12,experts=[5]; c7:bw=10,experts=[5]; c9:bw=50,experts=[0,1,2,4,5]; c2:bw=43,experts=[0,5,6,7]; c1:bw=10,experts=[0]; c5:bw=25,experts=[1,5]; c8:bw=18,experts=[0]; c3:bw=10,experts=[5]; c0:bw=31,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>11.7632,8.7945,15.5557,3.7464,9.2453,13.9862,2.8590,3.3204,1.6670,4.9914</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:58:50</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6411990598164644</v>
+      </c>
+      <c r="F26" t="n">
+        <v>92.01751690227412</v>
+      </c>
+      <c r="G26" t="n">
+        <v>92.01751690227412</v>
+      </c>
+      <c r="H26" t="n">
+        <v>25</v>
+      </c>
+      <c r="I26" t="n">
+        <v>79.76390000000001</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1:19.76</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>76.3687</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1689</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.2253</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2092.4716</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>34:52.47</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>9,6,4,3,5,1,8,2,0,7</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>9:40;6:16;4:58;3:14;5:64;1:49;8:55;2:12;0:56;7:40</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>9:[1,3,5,7];6:[4];4:[0,1,3,4,7];3:[0];5:[0,3,4,5,6,7];1:[0,3,4,5];8:[0,1,3,5,7];2:[6];0:[0,2,3,4,7];7:[0,4,5,7]</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>c9:bw=40,experts=[1,3,5,7]; c6:bw=16,experts=[4]; c4:bw=58,experts=[0,1,3,4,7]; c3:bw=14,experts=[0]; c5:bw=64,experts=[0,3,4,5,6,7]; c1:bw=49,experts=[0,3,4,5]; c8:bw=55,experts=[0,1,3,5,7]; c2:bw=12,experts=[6]; c0:bw=56,experts=[0,2,3,4,7]; c7:bw=40,experts=[0,4,5,7]</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>4.3044,11.9062,8.8222,1.4520,2.6842,14.5707,3.4753,9.4978,4.6148,15.0411</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:00:10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.6383228812474073</v>
+      </c>
+      <c r="F27" t="n">
+        <v>89.66656422864168</v>
+      </c>
+      <c r="G27" t="n">
+        <v>92.01751690227412</v>
+      </c>
+      <c r="H27" t="n">
+        <v>25</v>
+      </c>
+      <c r="I27" t="n">
+        <v>79.9701</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1:19.97</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>76.6045</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.2118</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2172.467</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>36:12.47</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>3,6,9,7,1,5,2,8,0,4</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>3:44;6:34;9:50;7:31;1:33;5:20;2:30;8:53;0:11;4:48</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>3:[0,1,6,7];6:[0,4,5];9:[1,2,4,6,7];7:[0,1,4];1:[1,5,6];5:[1,7];2:[3,6,7];8:[0,1,3,4,7];0:[7];4:[1,2,4,7]</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>c3:bw=44,experts=[0,1,6,7]; c6:bw=34,experts=[0,4,5]; c9:bw=50,experts=[1,2,4,6,7]; c7:bw=31,experts=[0,1,4]; c1:bw=33,experts=[1,5,6]; c5:bw=20,experts=[1,7]; c2:bw=30,experts=[3,6,7]; c8:bw=53,experts=[0,1,3,4,7]; c0:bw=11,experts=[7]; c4:bw=48,experts=[1,2,4,7]</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1.5989,11.9751,3.6336,15.7766,12.9760,2.7952,9.7818,3.3384,5.5303,9.1985</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:01:29</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6335241116679176</v>
+      </c>
+      <c r="F28" t="n">
+        <v>93.37738168408113</v>
+      </c>
+      <c r="G28" t="n">
+        <v>93.37738168408113</v>
+      </c>
+      <c r="H28" t="n">
+        <v>27</v>
+      </c>
+      <c r="I28" t="n">
+        <v>79.60420000000001</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1:19.60</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>76.1391</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1732</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.2909</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2252.0952</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>37:32.10</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>7,1,4,0,9,2,8,3,6,5</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>7:51;1:62;4:12;0:36;9:18;2:20;8:55;3:21;6:63;5:37</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>7:[0,2,3,6,7];1:[1,3,4,5,6,7];4:[3];0:[0,2,5];9:[2];2:[1,4];8:[0,3,4,5,7];3:[6,7];6:[0,1,2,4,5,6];5:[0,3,4]</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>c7:bw=51,experts=[0,2,3,6,7]; c1:bw=62,experts=[1,3,4,5,6,7]; c4:bw=12,experts=[3]; c0:bw=36,experts=[0,2,5]; c9:bw=18,experts=[2]; c2:bw=20,experts=[1,4]; c8:bw=55,experts=[0,3,4,5,7]; c3:bw=21,experts=[6,7]; c6:bw=63,experts=[0,1,2,4,5,6]; c5:bw=37,experts=[0,3,4]</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>15.9460,12.9352,9.0599,5.2466,3.8799,10.0715,2.9057,1.4889,11.4186,3.1869</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:02:48</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6303770266703588</v>
+      </c>
+      <c r="F29" t="n">
+        <v>92.94330055316533</v>
+      </c>
+      <c r="G29" t="n">
+        <v>93.37738168408113</v>
+      </c>
+      <c r="H29" t="n">
+        <v>27</v>
+      </c>
+      <c r="I29" t="n">
+        <v>79.211</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1:19.21</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>75.7439</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.1674</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.2988</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2331.3318</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>38:51.33</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>6,9,0,8,2,5,1,3,4,7</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>6:29;9:49;0:47;8:29;2:10;5:33;1:25;3:12;4:10;7:10</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>6:[2,4];9:[1,2,3,4];0:[0,2,4,7];8:[3,6];2:[7];5:[2,4,5];1:[4,6];3:[3];4:[2];7:[3]</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>c6:bw=29,experts=[2,4]; c9:bw=49,experts=[1,2,3,4]; c0:bw=47,experts=[0,2,4,7]; c8:bw=29,experts=[3,6]; c2:bw=10,experts=[7]; c5:bw=33,experts=[2,4,5]; c1:bw=25,experts=[4,6]; c3:bw=12,experts=[3]; c4:bw=10,experts=[2]; c7:bw=10,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>11.7066,3.4879,5.0937,3.2900,10.0345,2.8417,12.8619,1.4990,9.7498,15.1787</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:04:10</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6293165427619682</v>
+      </c>
+      <c r="F30" t="n">
+        <v>89.78180700676091</v>
+      </c>
+      <c r="G30" t="n">
+        <v>93.37738168408113</v>
+      </c>
+      <c r="H30" t="n">
+        <v>27</v>
+      </c>
+      <c r="I30" t="n">
+        <v>81.771</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1:21.77</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>78.2794</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.1787</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.312</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2413.1276</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>40:13.13</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>4,0,1,9,6,8,7,3,2,5</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>4:38;0:44;1:33;9:44;6:43;8:34;7:21;3:32;2:18;5:33</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>4:[1,4,5];0:[1,2,3,4];1:[2,4,7];9:[1,2,3,5];6:[0,1,4,6];8:[1,3,4];7:[1,5];3:[3,5,7];2:[2];5:[0,4,5]</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>c4:bw=38,experts=[1,4,5]; c0:bw=44,experts=[1,2,3,4]; c1:bw=33,experts=[2,4,7]; c9:bw=44,experts=[1,2,3,5]; c6:bw=43,experts=[0,1,4,6]; c8:bw=34,experts=[1,3,4]; c7:bw=21,experts=[1,5]; c3:bw=32,experts=[3,5,7]; c2:bw=18,experts=[2]; c5:bw=33,experts=[0,4,5]</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>9.9121,5.2834,14.0325,3.9086,11.7987,3.3344,15.7515,1.5738,9.7889,2.8954</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:05:32</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6247065663045304</v>
+      </c>
+      <c r="F31" t="n">
+        <v>89.20943454210203</v>
+      </c>
+      <c r="G31" t="n">
+        <v>93.37738168408113</v>
+      </c>
+      <c r="H31" t="n">
+        <v>27</v>
+      </c>
+      <c r="I31" t="n">
+        <v>81.261</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1:21.26</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>77.6713</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.278</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2494.413</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>41:34.41</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5,1,9,4,0,8,6,7,3,2</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>5:62;1:35;9:54;4:51;0:17;8:41;6:11;7:12;3:59;2:27</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>5:[0,1,2,5,6,7];1:[0,3,5];9:[0,3,4,5,7];4:[1,2,3,4,5];0:[4];8:[0,2,3,6];6:[7];7:[3];3:[0,2,3,5,7];2:[1,2]</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>c5:bw=62,experts=[0,1,2,5,6,7]; c1:bw=35,experts=[0,3,5]; c9:bw=54,experts=[0,3,4,5,7]; c4:bw=51,experts=[1,2,3,4,5]; c0:bw=17,experts=[4]; c8:bw=41,experts=[0,2,3,6]; c6:bw=11,experts=[7]; c7:bw=12,experts=[3]; c3:bw=59,experts=[0,2,3,5,7]; c2:bw=27,experts=[1,2]</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2.9465,13.9221,4.1578,9.6304,5.2467,3.3371,11.4105,15.4609,1.6112,9.9481</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:06:53</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6246885685109453</v>
+      </c>
+      <c r="F32" t="n">
+        <v>91.92916410571604</v>
+      </c>
+      <c r="G32" t="n">
+        <v>93.37738168408113</v>
+      </c>
+      <c r="H32" t="n">
+        <v>27</v>
+      </c>
+      <c r="I32" t="n">
+        <v>81.3931</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1:21.39</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>77.31010000000001</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.9209</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2575.833</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>42:55.83</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>6,4,9,1,5,8,3,2,0,7</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>6:29;4:19;9:45;1:30;5:62;8:33;3:24;2:15;0:47;7:63</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>6:[1,3];4:[1];9:[0,2,4,7];1:[0,1,6];5:[0,1,2,3,4,7];8:[4,5,6];3:[4,7];2:[1];0:[2,3,4,5];7:[0,1,2,4,5,6]</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>c6:bw=29,experts=[1,3]; c4:bw=19,experts=[1]; c9:bw=45,experts=[0,2,4,7]; c1:bw=30,experts=[0,1,6]; c5:bw=62,experts=[0,1,2,3,4,7]; c8:bw=33,experts=[4,5,6]; c3:bw=24,experts=[4,7]; c2:bw=15,experts=[1]; c0:bw=47,experts=[2,3,4,5]; c7:bw=63,experts=[0,1,2,4,5,6]</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>11.8223,9.2753,3.6248,13.9000,2.9138,3.3202,1.5749,9.5605,5.2102,16.1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:08:14</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.621376452550455</v>
+      </c>
+      <c r="F33" t="n">
+        <v>93.39274738783037</v>
+      </c>
+      <c r="G33" t="n">
+        <v>93.39274738783037</v>
+      </c>
+      <c r="H33" t="n">
+        <v>32</v>
+      </c>
+      <c r="I33" t="n">
+        <v>81.18429999999999</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1:21.18</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>77.7294</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.2938</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2657.0454</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>44:17.05</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>8,5,4,7,0,1,3,6,2,9</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>8:21;5:36;4:49;7:47;0:46;1:21;3:28;6:27;2:54;9:31</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>8:[1,3];5:[0,5,6];4:[0,2,4,7];7:[0,2,3,6];0:[0,2,5,6];1:[2,5];3:[2,3];6:[2,4];2:[0,2,5,6,7];9:[2,3,6]</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>c8:bw=21,experts=[1,3]; c5:bw=36,experts=[0,5,6]; c4:bw=49,experts=[0,2,4,7]; c7:bw=47,experts=[0,2,3,6]; c0:bw=46,experts=[0,2,5,6]; c1:bw=21,experts=[2,5]; c3:bw=28,experts=[2,3]; c6:bw=27,experts=[2,4]; c2:bw=54,experts=[0,2,5,6,7]; c9:bw=31,experts=[2,3,6]</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>3.5048,2.7437,9.0407,15.9840,5.6183,14.0577,1.5734,11.6847,9.6046,3.9177</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:09:34</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6188323541956064</v>
+      </c>
+      <c r="F34" t="n">
+        <v>94.25706822372464</v>
+      </c>
+      <c r="G34" t="n">
+        <v>94.25706822372464</v>
+      </c>
+      <c r="H34" t="n">
+        <v>33</v>
+      </c>
+      <c r="I34" t="n">
+        <v>80.1065</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1:20.11</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>76.6905</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.2344</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2737.1791</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>45:37.18</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>7,1,3,6,5,9,2,8,4,0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>7:52;1:34;3:70;6:37;5:29;9:42;2:24;8:50;4:45;0:62</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>7:[0,1,3,5,6];1:[2,6,7];3:[1,2,3,4,5,6,7];6:[0,1,2];5:[2,4];9:[0,2,3,6];2:[0,2];8:[0,1,4,5,6];4:[0,2,6,7];0:[0,1,3,4,5,6]</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>c7:bw=52,experts=[0,1,3,5,6]; c1:bw=34,experts=[2,6,7]; c3:bw=70,experts=[1,2,3,4,5,6,7]; c6:bw=37,experts=[0,1,2]; c5:bw=29,experts=[2,4]; c9:bw=42,experts=[0,2,3,6]; c2:bw=24,experts=[0,2]; c8:bw=50,experts=[0,1,4,5,6]; c4:bw=45,experts=[0,2,6,7]; c0:bw=62,experts=[0,1,3,4,5,6]</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>15.5942,13.8205,1.5103,11.8522,2.9587,3.5689,9.5147,3.3444,9.2268,5.2998</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:54</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6170419966028095</v>
+      </c>
+      <c r="F35" t="n">
+        <v>93.65012292563</v>
+      </c>
+      <c r="G35" t="n">
+        <v>94.25706822372464</v>
+      </c>
+      <c r="H35" t="n">
+        <v>33</v>
+      </c>
+      <c r="I35" t="n">
+        <v>79.7141</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1:19.71</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>76.3998</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.1751</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.1382</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2816.9213</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>46:56.92</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>4,1,6,9,8,0,5,7,3,2</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>4:46;1:46;6:48;9:68;8:42;0:22;5:60;7:32;3:72;2:54</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>4:[0,2,5,6];1:[2,3,5,6];6:[0,1,3,5];9:[2,3,4,5,6,7];8:[0,5,6,7];0:[2,5];5:[0,1,2,3,4,7];7:[1,2,5];3:[1,2,3,4,5,6,7];2:[0,1,4,5,6]</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>c4:bw=46,experts=[0,2,5,6]; c1:bw=46,experts=[2,3,5,6]; c6:bw=48,experts=[0,1,3,5]; c9:bw=68,experts=[2,3,4,5,6,7]; c8:bw=42,experts=[0,5,6,7]; c0:bw=22,experts=[2,5]; c5:bw=60,experts=[0,1,2,3,4,7]; c7:bw=32,experts=[1,2,5]; c3:bw=72,experts=[1,2,3,4,5,6,7]; c2:bw=54,experts=[0,1,4,5,6]</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>9.5294,14.2467,11.1730,3.3477,3.1763,5.0892,2.8980,15.7828,1.4817,9.6750</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:12:16</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6158102053040116</v>
+      </c>
+      <c r="F36" t="n">
+        <v>94.14182544560541</v>
+      </c>
+      <c r="G36" t="n">
+        <v>94.25706822372464</v>
+      </c>
+      <c r="H36" t="n">
+        <v>33</v>
+      </c>
+      <c r="I36" t="n">
+        <v>81.38639999999999</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1:21.39</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>77.8905</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.1736</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.3214</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2898.3352</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>48:18.34</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>4,0,1,6,2,8,9,7,5,3</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>4:33;0:20;1:31;6:44;2:46;8:50;9:27;7:48;5:41;3:24</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>4:[2,3,7];0:[2,5];1:[1,2,3];6:[3,5,6,7];2:[0,2,4,5];8:[0,2,4,5,6];9:[0,6];7:[0,4,6,7];5:[0,3,6,7];3:[2,5]</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>c4:bw=33,experts=[2,3,7]; c0:bw=20,experts=[2,5]; c1:bw=31,experts=[1,2,3]; c6:bw=44,experts=[3,5,6,7]; c2:bw=46,experts=[0,2,4,5]; c8:bw=50,experts=[0,2,4,5,6]; c9:bw=27,experts=[0,6]; c7:bw=48,experts=[0,4,6,7]; c5:bw=41,experts=[0,3,6,7]; c3:bw=24,experts=[2,5]</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>9.6748,5.3125,14.1055,11.8065,9.2914,3.2092,3.7989,15.8020,3.1948,1.6949</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:36</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.612804780361718</v>
+      </c>
+      <c r="F37" t="n">
+        <v>93.51951444376152</v>
+      </c>
+      <c r="G37" t="n">
+        <v>94.25706822372464</v>
+      </c>
+      <c r="H37" t="n">
+        <v>33</v>
+      </c>
+      <c r="I37" t="n">
+        <v>80.6294</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1:20.63</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>77.13</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.1639</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.3345</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2978.9919</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>49:38.99</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>9,0,3,7,6,5,1,4,8,2</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>9:37;0:36;3:60;7:27;6:43;5:49;1:10;4:74;8:51;2:50</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>9:[1,3,5];0:[0,2,3];3:[1,2,3,4,6,7];7:[5,7];6:[0,5,6,7];5:[1,5,6,7];1:[0];4:[0,1,2,3,4,6,7];8:[0,2,3,5,7];2:[0,1,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>c9:bw=37,experts=[1,3,5]; c0:bw=36,experts=[0,2,3]; c3:bw=60,experts=[1,2,3,4,6,7]; c7:bw=27,experts=[5,7]; c6:bw=43,experts=[0,5,6,7]; c5:bw=49,experts=[1,5,6,7]; c1:bw=10,experts=[0]; c4:bw=74,experts=[0,1,2,3,4,6,7]; c8:bw=51,experts=[0,2,3,5,7]; c2:bw=50,experts=[0,1,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>3.5016,5.0855,1.5227,15.8382,11.4313,2.9202,14.5088,9.3088,3.1873,9.8255</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:57</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6147009896182192</v>
+      </c>
+      <c r="F38" t="n">
+        <v>93.57713583282114</v>
+      </c>
+      <c r="G38" t="n">
+        <v>94.25706822372464</v>
+      </c>
+      <c r="H38" t="n">
+        <v>33</v>
+      </c>
+      <c r="I38" t="n">
+        <v>81.2302</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1:21.23</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>77.9272</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.1243</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3060.2513</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>51:00.25</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1,5,2,6,4,7,9,0,3,8</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1:18;5:39;2:36;6:65;4:39;7:42;9:40;0:54;3:36;8:10</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1:[0];5:[0,1,5];2:[0,2,3];6:[0,1,3,4,5,7];4:[0,1,3];7:[0,3,6,7];9:[0,1,4,5];0:[0,2,3,5,7];3:[1,6,7];8:[0]</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>c1:bw=18,experts=[0]; c5:bw=39,experts=[0,1,5]; c2:bw=36,experts=[0,2,3]; c6:bw=65,experts=[0,1,3,4,5,7]; c4:bw=39,experts=[0,1,3]; c7:bw=42,experts=[0,3,6,7]; c9:bw=40,experts=[0,1,4,5]; c0:bw=54,experts=[0,2,3,5,7]; c3:bw=36,experts=[1,6,7]; c8:bw=10,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>14.3417,2.8435,10.3318,11.7151,8.8897,15.5671,3.9193,5.2958,1.5910,3.4320</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:16:17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6119341849794002</v>
+      </c>
+      <c r="F39" t="n">
+        <v>93.44268592501537</v>
+      </c>
+      <c r="G39" t="n">
+        <v>94.25706822372464</v>
+      </c>
+      <c r="H39" t="n">
+        <v>33</v>
+      </c>
+      <c r="I39" t="n">
+        <v>79.19499999999999</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1:19.19</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>75.7552</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.2717</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3139.4718</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>52:19.47</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>8,6,4,1,5,2,3,7,9,0</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>8:46;6:17;4:52;1:31;5:10;2:10;3:38;7:51;9:26;0:40</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>8:[1,2,5,6];6:[5];4:[1,2,3,6,7];1:[1,2,6];5:[6];2:[4];3:[2,5,7];7:[0,1,3,6,7];9:[0,6];0:[1,2,6,7]</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>c8:bw=46,experts=[1,2,5,6]; c6:bw=17,experts=[5]; c4:bw=52,experts=[1,2,3,6,7]; c1:bw=31,experts=[1,2,6]; c5:bw=10,experts=[6]; c2:bw=10,experts=[4]; c3:bw=38,experts=[2,5,7]; c7:bw=51,experts=[0,1,3,6,7]; c9:bw=26,experts=[0,6]; c0:bw=40,experts=[1,2,6,7]</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>3.1345,11.8812,9.2368,13.2637,2.8388,9.7456,1.5610,14.9715,3.8543,5.2678</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:17:37</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6105278610523748</v>
+      </c>
+      <c r="F40" t="n">
+        <v>93.81146281499693</v>
+      </c>
+      <c r="G40" t="n">
+        <v>94.25706822372464</v>
+      </c>
+      <c r="H40" t="n">
+        <v>33</v>
+      </c>
+      <c r="I40" t="n">
+        <v>80.5972</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1:20.60</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>77.4213</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.0187</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3220.0986</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>53:40.10</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3,0,1,7,6,8,2,4,9,5</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3:26;0:10;1:45;7:40;6:31;8:45;2:36;4:36;9:24;5:75</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3:[3,6];0:[3];1:[3,5,6,7];7:[1,2,4,5];6:[0,1,6];8:[0,1,2,4];2:[0,1,3];4:[2,3,6];9:[3,6];5:[0,2,3,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>c3:bw=26,experts=[3,6]; c0:bw=10,experts=[3]; c1:bw=45,experts=[3,5,6,7]; c7:bw=40,experts=[1,2,4,5]; c6:bw=31,experts=[0,1,6]; c8:bw=45,experts=[0,1,2,4]; c2:bw=36,experts=[0,1,3]; c4:bw=36,experts=[2,3,6]; c9:bw=24,experts=[3,6]; c5:bw=75,experts=[0,2,3,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1.5269,5.2813,13.6784,16.6668,11.3322,3.3993,10.1016,8.9429,3.6974,2.7945</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:18:57</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6129692800937189</v>
+      </c>
+      <c r="F41" t="n">
+        <v>94.24554394591273</v>
+      </c>
+      <c r="G41" t="n">
+        <v>94.25706822372464</v>
+      </c>
+      <c r="H41" t="n">
+        <v>33</v>
+      </c>
+      <c r="I41" t="n">
+        <v>79.8802</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1:19.88</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>76.4299</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.1781</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.2713</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3300.0086</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>55:00.01</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>8,1,5,6,2,7,3,4,9,0</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>8:26;1:42;5:32;6:46;2:65;7:66;3:10;4:19;9:40;0:36</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8:[0,7];1:[0,2,3,4];5:[5,6,7];6:[0,2,3,5];2:[1,2,4,5,6,7];7:[0,1,2,3,6,7];3:[7];4:[2];9:[3,5,6,7];0:[3,4,7]</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>c8:bw=26,experts=[0,7]; c1:bw=42,experts=[0,2,3,4]; c5:bw=32,experts=[5,6,7]; c6:bw=46,experts=[0,2,3,5]; c2:bw=65,experts=[1,2,4,5,6,7]; c7:bw=66,experts=[0,1,2,3,6,7]; c3:bw=10,experts=[7]; c4:bw=19,experts=[2]; c9:bw=40,experts=[3,5,6,7]; c0:bw=36,experts=[3,4,7]</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>3.3720,13.6330,2.7354,11.0359,9.9931,15.8090,1.5700,8.9269,4.0112,5.3431</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:20:17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.609315003450089</v>
+      </c>
+      <c r="F42" t="n">
+        <v>92.80116779348494</v>
+      </c>
+      <c r="G42" t="n">
+        <v>94.25706822372464</v>
+      </c>
+      <c r="H42" t="n">
+        <v>33</v>
+      </c>
+      <c r="I42" t="n">
+        <v>80.0779</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1:20.08</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>76.9335</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.985</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3380.1144</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>56:20.11</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2,6,8,1,4,5,7,3,9,0</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2:54;6:10;8:57;1:10;4:50;5:61;7:68;3:40;9:54;0:10</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2:[1,2,3,4,5];6:[3];8:[1,2,3,5,7];1:[7];4:[0,2,3,6,7];5:[0,2,3,5,6,7];7:[0,1,2,4,5,7];3:[0,1,2,3];9:[0,1,2,6,7];0:[2]</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>c2:bw=54,experts=[1,2,3,4,5]; c6:bw=10,experts=[3]; c8:bw=57,experts=[1,2,3,5,7]; c1:bw=10,experts=[7]; c4:bw=50,experts=[0,2,3,6,7]; c5:bw=61,experts=[0,2,3,5,6,7]; c7:bw=68,experts=[0,1,2,4,5,7]; c3:bw=40,experts=[0,1,2,3]; c9:bw=54,experts=[0,1,2,6,7]; c0:bw=10,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>9.9514,11.3774,3.3673,14.2308,8.4956,2.8792,15.8109,1.6808,3.8941,5.2459</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:21:38</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6065826443321212</v>
+      </c>
+      <c r="F43" t="n">
+        <v>94.16487400122925</v>
+      </c>
+      <c r="G43" t="n">
+        <v>94.25706822372464</v>
+      </c>
+      <c r="H43" t="n">
+        <v>33</v>
+      </c>
+      <c r="I43" t="n">
+        <v>80.4404</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1:20.44</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>77.1275</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.1565</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3460.5842</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>57:40.58</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5,1,3,9,6,0,7,4,8,2</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>5:50;1:49;3:48;9:51;6:34;0:15;7:20;4:55;8:42;2:40</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>5:[1,2,3,5,7];1:[3,4,5,7];3:[0,1,3,4];9:[1,3,4,6,7];6:[3,4,7];0:[3];7:[2,4];4:[1,2,4,5,6];8:[2,3,5,7];2:[0,2,4,6]</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>c5:bw=50,experts=[1,2,3,5,7]; c1:bw=49,experts=[3,4,5,7]; c3:bw=48,experts=[0,1,3,4]; c9:bw=51,experts=[1,3,4,6,7]; c6:bw=34,experts=[3,4,7]; c0:bw=15,experts=[3]; c7:bw=20,experts=[2,4]; c4:bw=55,experts=[1,2,4,5,6]; c8:bw=42,experts=[2,3,5,7]; c2:bw=40,experts=[0,2,4,6]</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2.9561,14.4124,1.6239,3.9225,11.4355,5.0261,15.6344,8.7492,3.3467,10.0206</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:23:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.6060810877237616</v>
+      </c>
+      <c r="F44" t="n">
+        <v>94.00737553779963</v>
+      </c>
+      <c r="G44" t="n">
+        <v>94.25706822372464</v>
+      </c>
+      <c r="H44" t="n">
+        <v>33</v>
+      </c>
+      <c r="I44" t="n">
+        <v>82.3215</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1:22.32</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>78.8154</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.3379</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3542.9359</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>59:02.94</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5,1,2,8,9,7,4,6,3,0</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>5:53;1:58;2:51;8:45;9:32;7:21;4:34;6:12;3:65;0:21</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>5:[1,2,4,6,7];1:[0,1,3,5,7];2:[0,2,3,4,5];8:[0,2,4,5];9:[1,3,4];7:[2,7];4:[4,6,7];6:[6];3:[0,1,2,4,5,7];0:[3,4]</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>c5:bw=53,experts=[1,2,4,6,7]; c1:bw=58,experts=[0,1,3,5,7]; c2:bw=51,experts=[0,2,3,4,5]; c8:bw=45,experts=[0,2,4,5]; c9:bw=32,experts=[1,3,4]; c7:bw=21,experts=[2,7]; c4:bw=34,experts=[4,6,7]; c6:bw=12,experts=[6]; c3:bw=65,experts=[0,1,2,4,5,7]; c0:bw=21,experts=[3,4]</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2.8336,13.5092,9.9405,3.6529,4.1562,16.0310,9.8308,12.4289,1.6040,4.8284</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:24:22</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6059752736243593</v>
+      </c>
+      <c r="F45" t="n">
+        <v>94.29548248309773</v>
+      </c>
+      <c r="G45" t="n">
+        <v>94.29548248309773</v>
+      </c>
+      <c r="H45" t="n">
+        <v>44</v>
+      </c>
+      <c r="I45" t="n">
+        <v>81.4365</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1:21.44</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>78.06100000000001</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.1726</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.202</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3624.4027</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1:00:24.40</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>0,3,4,2,7,5,6,9,8,1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>0:66;3:47;4:29;2:37;7:75;5:24;6:20;9:37;8:34;1:45</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0:[0,2,3,5,6,7];3:[1,3,4,7];4:[1,5];2:[0,2,5];7:[0,1,2,3,4,6,7];5:[2,4];6:[4,6];9:[3,5,7];8:[2,4,7];1:[1,2,5,7]</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>c0:bw=66,experts=[0,2,3,5,6,7]; c3:bw=47,experts=[1,3,4,7]; c4:bw=29,experts=[1,5]; c2:bw=37,experts=[0,2,5]; c7:bw=75,experts=[0,1,2,3,4,6,7]; c5:bw=24,experts=[2,4]; c6:bw=20,experts=[4,6]; c9:bw=37,experts=[3,5,7]; c8:bw=34,experts=[2,4,7]; c1:bw=45,experts=[1,2,5,7]</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>5.2287,1.5709,9.1384,9.8282,15.9597,2.8573,11.4214,3.9288,3.7445,14.3830</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:25:41</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.6047348818316347</v>
+      </c>
+      <c r="F46" t="n">
+        <v>94.16103257529196</v>
+      </c>
+      <c r="G46" t="n">
+        <v>94.29548248309773</v>
+      </c>
+      <c r="H46" t="n">
+        <v>44</v>
+      </c>
+      <c r="I46" t="n">
+        <v>79.5086</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1:19.51</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>76.12820000000001</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.2051</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3703.9411</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1:01:43.94</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8,0,3,4,7,2,9,6,5,1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>8:55;0:36;3:67;4:64;7:36;2:49;9:25;6:10;5:44;1:56</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>8:[0,2,3,5,6];0:[3,4,6];3:[0,1,2,3,4,5];4:[0,1,3,4,5,7];7:[0,5,6];2:[1,4,6,7];9:[3,6];6:[0];5:[1,3,4,7];1:[0,1,2,3,7]</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>c8:bw=55,experts=[0,2,3,5,6]; c0:bw=36,experts=[3,4,6]; c3:bw=67,experts=[0,1,2,3,4,5]; c4:bw=64,experts=[0,1,3,4,5,7]; c7:bw=36,experts=[0,5,6]; c2:bw=49,experts=[1,4,6,7]; c9:bw=25,experts=[3,6]; c6:bw=10,experts=[0]; c5:bw=44,experts=[1,3,4,7]; c1:bw=56,experts=[0,1,2,3,7]</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>3.3813,4.9459,1.6288,9.2288,15.7145,9.0534,3.8821,11.8833,2.8564,13.5536</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:27:04</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.6045321994478756</v>
+      </c>
+      <c r="F47" t="n">
+        <v>93.46957590657652</v>
+      </c>
+      <c r="G47" t="n">
+        <v>94.29548248309773</v>
+      </c>
+      <c r="H47" t="n">
+        <v>44</v>
+      </c>
+      <c r="I47" t="n">
+        <v>83.0667</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1:23.07</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>79.55110000000001</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.3404</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3787.0396</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>1:03:07.04</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>9,3,6,1,4,5,2,8,0,7</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>9:37;3:27;6:39;1:41;4:64;5:41;2:57;8:39;0:55;7:28</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>9:[2,5,6];3:[1,5];6:[2,5,6];1:[3,4,5,7];4:[0,1,3,4,5,6];5:[0,4,5,6];2:[0,1,2,5,7];8:[1,3,6];0:[1,2,5,6,7];7:[0,7]</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>c9:bw=37,experts=[2,5,6]; c3:bw=27,experts=[1,5]; c6:bw=39,experts=[2,5,6]; c1:bw=41,experts=[3,4,5,7]; c4:bw=64,experts=[0,1,3,4,5,6]; c5:bw=41,experts=[0,4,5,6]; c2:bw=57,experts=[0,1,2,5,7]; c8:bw=39,experts=[1,3,6]; c0:bw=55,experts=[1,2,5,6,7]; c7:bw=28,experts=[0,7]</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>3.9858,1.6303,11.9936,13.9370,9.6592,3.3128,10.3558,3.6327,5.3263,15.7176</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:28:25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.6030275241282999</v>
+      </c>
+      <c r="F48" t="n">
+        <v>94.89474492931777</v>
+      </c>
+      <c r="G48" t="n">
+        <v>94.89474492931777</v>
+      </c>
+      <c r="H48" t="n">
+        <v>47</v>
+      </c>
+      <c r="I48" t="n">
+        <v>80.73869999999999</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1:20.74</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>77.309</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.2633</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3867.8107</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1:04:27.81</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>5,6,7,9,8,3,4,0,1,2</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>5:52;6:22;7:53;9:17;8:39;3:70;4:10;0:46;1:30;2:54</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>5:[0,2,3,6,7];6:[0,1];7:[0,1,5,6,7];9:[7];8:[4,5,7];3:[0,1,2,4,5,6,7];4:[1];0:[2,4,5,7];1:[0,1,7];2:[0,1,2,6,7]</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>c5:bw=52,experts=[0,2,3,6,7]; c6:bw=22,experts=[0,1]; c7:bw=53,experts=[0,1,5,6,7]; c9:bw=17,experts=[7]; c8:bw=39,experts=[4,5,7]; c3:bw=70,experts=[0,1,2,4,5,6,7]; c4:bw=10,experts=[1]; c0:bw=46,experts=[2,4,5,7]; c1:bw=30,experts=[0,1,7]; c2:bw=54,experts=[0,1,2,6,7]</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2.7516,11.8382,15.9438,3.5397,3.3449,1.6270,9.1436,5.2791,13.7488,10.0923</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:29:47</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6024232432360849</v>
+      </c>
+      <c r="F49" t="n">
+        <v>94.29548248309773</v>
+      </c>
+      <c r="G49" t="n">
+        <v>94.89474492931777</v>
+      </c>
+      <c r="H49" t="n">
+        <v>47</v>
+      </c>
+      <c r="I49" t="n">
+        <v>81.9421</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1:21.94</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>78.70820000000001</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.0761</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3949.7843</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>1:05:49.78</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1,8,4,2,9,6,5,7,0,3</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1:50;8:50;4:67;2:57;9:52;6:45;5:55;7:62;0:16;3:18</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1:[1,3,4,5,7];8:[1,3,4,5,7];4:[0,1,2,5,6,7];2:[0,2,3,5,7];9:[1,4,5,6,7];6:[0,4,5,7];5:[2,3,4,6,7];7:[0,1,3,4,5,6];0:[5];3:[1]</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>c1:bw=50,experts=[1,3,4,5,7]; c8:bw=50,experts=[1,3,4,5,7]; c4:bw=67,experts=[0,1,2,5,6,7]; c2:bw=57,experts=[0,2,3,5,7]; c9:bw=52,experts=[1,4,5,6,7]; c6:bw=45,experts=[0,4,5,7]; c5:bw=55,experts=[2,3,4,6,7]; c7:bw=62,experts=[0,1,3,4,5,6]; c0:bw=16,experts=[5]; c3:bw=18,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>14.5901,3.0233,9.0270,10.2184,3.9013,11.4358,3.0724,16.7479,5.1359,1.5561</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:31:08</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.5999929370812629</v>
+      </c>
+      <c r="F50" t="n">
+        <v>94.1379840196681</v>
+      </c>
+      <c r="G50" t="n">
+        <v>94.89474492931777</v>
+      </c>
+      <c r="H50" t="n">
+        <v>47</v>
+      </c>
+      <c r="I50" t="n">
+        <v>80.71339999999999</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1:20.71</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>77.22410000000001</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.3219</v>
+      </c>
+      <c r="N50" t="n">
+        <v>4030.5316</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>1:07:10.53</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>4,3,8,0,2,5,6,7,9,1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>4:48;3:32;8:26;0:20;2:58;5:56;6:13;7:44;9:53;1:54</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>4:[0,1,4,5];3:[0,3,5];8:[0,4];0:[1,6];2:[0,2,3,4,5];5:[2,4,5,6,7];6:[3];7:[0,5,6,7];9:[0,1,2,6,7];1:[1,2,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>c4:bw=48,experts=[0,1,4,5]; c3:bw=32,experts=[0,3,5]; c8:bw=26,experts=[0,4]; c0:bw=20,experts=[1,6]; c2:bw=58,experts=[0,2,3,4,5]; c5:bw=56,experts=[2,4,5,6,7]; c6:bw=13,experts=[3]; c7:bw=44,experts=[0,5,6,7]; c9:bw=53,experts=[0,1,2,6,7]; c1:bw=54,experts=[1,2,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>9.2972,1.6100,3.3884,5.2977,9.7691,2.7995,11.3684,15.8233,4.0406,13.8298</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:32:28</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.6007096966401901</v>
+      </c>
+      <c r="F51" t="n">
+        <v>94.66425937307929</v>
+      </c>
+      <c r="G51" t="n">
+        <v>94.89474492931777</v>
+      </c>
+      <c r="H51" t="n">
+        <v>47</v>
+      </c>
+      <c r="I51" t="n">
+        <v>80.2132</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1:20.21</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>77.1658</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.8961</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4110.7786</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1:08:30.78</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>8,4,7,6,2,1,3,0,9,5</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>8:32;4:10;7:34;6:68;2:63;1:64;3:39;0:29;9:27;5:31</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>8:[3,4,5];4:[0];7:[3,4,5];6:[0,1,2,3,5,7];2:[0,1,2,3,6,7];1:[0,1,4,5,6,7];3:[0,3,4];0:[1,2];9:[4,5];5:[2,3,5]</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>c8:bw=32,experts=[3,4,5]; c4:bw=10,experts=[0]; c7:bw=34,experts=[3,4,5]; c6:bw=68,experts=[0,1,2,3,5,7]; c2:bw=63,experts=[0,1,2,3,6,7]; c1:bw=64,experts=[0,1,4,5,6,7]; c3:bw=39,experts=[0,3,4]; c0:bw=29,experts=[1,2]; c9:bw=27,experts=[4,5]; c5:bw=31,experts=[2,3,5]</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>3.3884,9.2097,15.4362,11.9175,9.8430,14.2557,1.6002,5.0562,3.6926,2.7663</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:33:48</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.5989304146356961</v>
+      </c>
+      <c r="F52" t="n">
+        <v>94.30700676090964</v>
+      </c>
+      <c r="G52" t="n">
+        <v>94.89474492931777</v>
+      </c>
+      <c r="H52" t="n">
+        <v>47</v>
+      </c>
+      <c r="I52" t="n">
+        <v>79.7659</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1:19.77</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>76.32689999999999</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.2611</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4190.5761</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>1:09:50.58</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>5,0,1,2,8,6,9,3,4,7</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>5:47;0:53;1:21;2:20;8:46;6:52;9:18;3:55;4:11;7:27</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>5:[2,3,5,7];0:[0,2,3,5,7];1:[4,6];2:[5,7];8:[0,1,2,4];6:[0,1,3,4,7];9:[2];3:[1,3,5,6,7];4:[3];7:[0,3]</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>c5:bw=47,experts=[2,3,5,7]; c0:bw=53,experts=[0,2,3,5,7]; c1:bw=21,experts=[4,6]; c2:bw=20,experts=[5,7]; c8:bw=46,experts=[0,1,2,4]; c6:bw=52,experts=[0,1,3,4,7]; c9:bw=18,experts=[2]; c3:bw=55,experts=[1,3,5,6,7]; c4:bw=11,experts=[3]; c7:bw=27,experts=[0,3]</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2.8852,5.4084,13.9625,9.7935,3.3017,11.6843,3.8838,1.5778,8.8648,14.9648</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:35:09</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.5987194086856147</v>
+      </c>
+      <c r="F53" t="n">
+        <v>94.54133374308543</v>
+      </c>
+      <c r="G53" t="n">
+        <v>94.89474492931777</v>
+      </c>
+      <c r="H53" t="n">
+        <v>47</v>
+      </c>
+      <c r="I53" t="n">
+        <v>80.8969</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1:20.90</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>77.4329</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.1621</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.301</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4271.5085</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1:11:11.51</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>0,8,5,7,1,4,9,6,2,3</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>0:46;8:18;5:24;7:34;1:40;4:33;9:31;6:51;2:29;3:43</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0:[0,1,3,5];8:[7];5:[0,7];7:[2,4,6];1:[0,1,4,7];4:[3,5,7];9:[2,4,6];6:[0,2,4,5,6];2:[2,4];3:[0,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>c0:bw=46,experts=[0,1,3,5]; c8:bw=18,experts=[7]; c5:bw=24,experts=[0,7]; c7:bw=34,experts=[2,4,6]; c1:bw=40,experts=[0,1,4,7]; c4:bw=33,experts=[3,5,7]; c9:bw=31,experts=[2,4,6]; c6:bw=51,experts=[0,2,4,5,6]; c2:bw=29,experts=[2,4]; c3:bw=43,experts=[0,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>5.6901,3.7998,2.9820,15.6413,13.8161,8.6778,4.1790,11.6479,9.5134,1.4855</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:36:30</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5980896763318058</v>
+      </c>
+      <c r="F54" t="n">
+        <v>94.21481253841426</v>
+      </c>
+      <c r="G54" t="n">
+        <v>94.89474492931777</v>
+      </c>
+      <c r="H54" t="n">
+        <v>47</v>
+      </c>
+      <c r="I54" t="n">
+        <v>81.2946</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1:21.29</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>77.8212</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.2986</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4352.8366</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1:12:32.84</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>8,4,5,1,3,9,6,7,0,2</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>8:22;4:28;5:44;1:59;3:47;9:61;6:36;7:44;0:39;2:51</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>8:[0,2];4:[3,6];5:[1,2,3,5];1:[1,2,3,4,7];3:[0,1,3,4];9:[1,2,4,5,6,7];6:[0,2,7];7:[1,2,4,5];0:[0,2,5];2:[0,1,2,3,4]</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>c8:bw=22,experts=[0,2]; c4:bw=28,experts=[3,6]; c5:bw=44,experts=[1,2,3,5]; c1:bw=59,experts=[1,2,3,4,7]; c3:bw=47,experts=[0,1,3,4]; c9:bw=61,experts=[1,2,4,5,6,7]; c6:bw=36,experts=[0,2,7]; c7:bw=44,experts=[1,2,4,5]; c0:bw=39,experts=[0,2,5]; c2:bw=51,experts=[0,1,2,3,4]</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>3.5381,9.3312,3.2925,13.5039,1.3251,3.8612,11.5748,15.3778,5.4908,10.5259</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:37:50</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.5968018037455468</v>
+      </c>
+      <c r="F55" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="G55" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H55" t="n">
+        <v>54</v>
+      </c>
+      <c r="I55" t="n">
+        <v>80.295</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1:20.30</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>76.9118</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.221</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4433.1648</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1:13:53.16</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2,1,8,7,3,0,6,5,9,4</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2:10;1:53;8:55;7:61;3:30;0:37;6:54;5:10;9:50;4:32</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2:[0];1:[0,1,2,5,6];8:[0,2,4,6,7];7:[1,2,3,4,5,6];3:[1,4,5];0:[0,3,5];6:[1,2,3,5,7];5:[6];9:[2,3,4,5,7];4:[2,4,5]</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>c2:bw=10,experts=[0]; c1:bw=53,experts=[0,1,2,5,6]; c8:bw=55,experts=[0,2,4,6,7]; c7:bw=61,experts=[1,2,3,4,5,6]; c3:bw=30,experts=[1,4,5]; c0:bw=37,experts=[0,3,5]; c6:bw=54,experts=[1,2,3,5,7]; c5:bw=10,experts=[6]; c9:bw=50,experts=[2,3,4,5,7]; c4:bw=32,experts=[2,4,5]</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>10.3316,13.6898,3.3557,15.5666,1.5287,5.0132,11.6869,2.9135,4.0104,8.8155</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:39:11</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.5952149535399071</v>
+      </c>
+      <c r="F56" t="n">
+        <v>92.45159803318992</v>
+      </c>
+      <c r="G56" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H56" t="n">
+        <v>54</v>
+      </c>
+      <c r="I56" t="n">
+        <v>80.5595</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1:20.56</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>77.0796</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.308</v>
+      </c>
+      <c r="N56" t="n">
+        <v>4513.7586</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1:15:13.76</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>7,2,4,3,8,5,1,6,0,9</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>7:54;2:41;4:14;3:52;8:14;5:53;1:60;6:42;0:27;9:62</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>7:[1,3,4,6,7];2:[1,4,5,7];4:[1];3:[0,2,3,5,7];8:[1];5:[0,1,2,3,5];1:[1,2,3,5,6,7];6:[1,3,4,7];0:[4,6];9:[0,2,3,4,5,7]</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>c7:bw=54,experts=[1,3,4,6,7]; c2:bw=41,experts=[1,4,5,7]; c4:bw=14,experts=[1]; c3:bw=52,experts=[0,2,3,5,7]; c8:bw=14,experts=[1]; c5:bw=53,experts=[0,1,2,3,5]; c1:bw=60,experts=[1,2,3,5,6,7]; c6:bw=42,experts=[1,3,4,7]; c0:bw=27,experts=[4,6]; c9:bw=62,experts=[0,2,3,4,5,7]</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>16.1975,9.5785,8.9134,1.6077,3.3456,2.9531,13.8909,11.3998,5.2692,3.9239</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:40:33</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.5925721198731146</v>
+      </c>
+      <c r="F57" t="n">
+        <v>93.19299323909036</v>
+      </c>
+      <c r="G57" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H57" t="n">
+        <v>54</v>
+      </c>
+      <c r="I57" t="n">
+        <v>81.97280000000001</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1:21.97</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>77.881</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.1712</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.9196</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4595.7659</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1:16:35.77</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>9,1,3,2,5,4,8,7,6,0</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>9:52;1:56;3:10;2:53;5:31;4:10;8:13;7:18;6:23;0:70</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>9:[1,3,4,5,6];1:[1,2,5,6,7];3:[4];2:[0,3,4,5,6];5:[3,5,6];4:[7];8:[1];7:[2];6:[3,6];0:[0,1,2,3,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>c9:bw=52,experts=[1,3,4,5,6]; c1:bw=56,experts=[1,2,5,6,7]; c3:bw=10,experts=[4]; c2:bw=53,experts=[0,3,4,5,6]; c5:bw=31,experts=[3,5,6]; c4:bw=10,experts=[7]; c8:bw=13,experts=[1]; c7:bw=18,experts=[2]; c6:bw=23,experts=[3,6]; c0:bw=70,experts=[0,1,2,3,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>4.0058,13.9578,1.7856,10.2836,2.9150,8.7231,3.3275,16.1930,11.2988,5.3907</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:41:53</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.5932380958471806</v>
+      </c>
+      <c r="F58" t="n">
+        <v>94.17639827904118</v>
+      </c>
+      <c r="G58" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H58" t="n">
+        <v>54</v>
+      </c>
+      <c r="I58" t="n">
+        <v>79.6935</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1:19.69</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>76.22199999999999</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.1804</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.2901</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4675.4944</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>1:17:55.49</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>3,8,6,1,7,0,5,4,2,9</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>3:64;8:43;6:48;1:49;7:69;0:70;5:44;4:41;2:33;9:19</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>3:[0,1,2,4,5,6];8:[1,3,5,7];6:[1,2,4,5];1:[1,2,4,5];7:[0,1,2,3,4,7];0:[0,1,2,3,5,6,7];5:[2,3,5,7];4:[0,1,3,4];2:[0,4,5];9:[6]</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>c3:bw=64,experts=[0,1,2,4,5,6]; c8:bw=43,experts=[1,3,5,7]; c6:bw=48,experts=[1,2,4,5]; c1:bw=49,experts=[1,2,4,5]; c7:bw=69,experts=[0,1,2,3,4,7]; c0:bw=70,experts=[0,1,2,3,5,6,7]; c5:bw=44,experts=[2,3,5,7]; c4:bw=41,experts=[0,1,3,4]; c2:bw=33,experts=[0,4,5]; c9:bw=19,experts=[6]</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>1.6143,3.3623,11.8452,13.1466,15.7930,5.0645,2.7868,8.7976,9.9480,3.8635</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:43:15</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.5927554144765195</v>
+      </c>
+      <c r="F59" t="n">
+        <v>94.97541487400123</v>
+      </c>
+      <c r="G59" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H59" t="n">
+        <v>54</v>
+      </c>
+      <c r="I59" t="n">
+        <v>82.2564</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>1:22.26</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>78.7944</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3.2933</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4757.7854</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1:19:17.79</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>7,2,9,6,5,1,8,4,3,0</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>7:24;2:10;9:57;6:55;5:35;1:30;8:40;4:38;3:61;0:47</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>7:[1,7];2:[3];9:[0,1,3,4,6];6:[0,1,3,4,7];5:[2,3,6];1:[4,5,6];8:[0,2,4,7];4:[0,4,5];3:[0,2,3,4,5,6];0:[0,2,6,7]</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>c7:bw=24,experts=[1,7]; c2:bw=10,experts=[3]; c9:bw=57,experts=[0,1,3,4,6]; c6:bw=55,experts=[0,1,3,4,7]; c5:bw=35,experts=[2,3,6]; c1:bw=30,experts=[4,5,6]; c8:bw=40,experts=[0,2,4,7]; c4:bw=38,experts=[0,4,5]; c3:bw=61,experts=[0,2,3,4,5,6]; c0:bw=47,experts=[0,2,6,7]</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>16.0924,10.5744,3.9406,11.5562,2.9213,14.2485,3.3971,9.1164,1.6158,5.3316</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:44:40</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.5911505310725819</v>
+      </c>
+      <c r="F60" t="n">
+        <v>95.07529194837123</v>
+      </c>
+      <c r="G60" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H60" t="n">
+        <v>54</v>
+      </c>
+      <c r="I60" t="n">
+        <v>85.13339999999999</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1:25.13</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>81.5663</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.2303</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.3359</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4842.9539</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1:20:42.95</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2,8,9,6,1,4,7,5,0,3</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2:37;8:56;9:28;6:19;1:65;4:26;7:28;5:32;0:52;3:35</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2:[3,6,7];8:[0,1,2,4,6];9:[4,6];6:[1];1:[0,2,3,4,6,7];4:[2,6];7:[3,5];5:[0,4,7];0:[0,1,2,4,6];3:[0,3,6]</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>c2:bw=37,experts=[3,6,7]; c8:bw=56,experts=[0,1,2,4,6]; c9:bw=28,experts=[4,6]; c6:bw=19,experts=[1]; c1:bw=65,experts=[0,2,3,4,6,7]; c4:bw=26,experts=[2,6]; c7:bw=28,experts=[3,5]; c5:bw=32,experts=[0,4,7]; c0:bw=52,experts=[0,1,2,4,6]; c3:bw=35,experts=[0,3,6]</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>10.1724,3.6241,4.0239,14.6172,13.8990,8.7205,15.7324,3.2093,5.8341,1.7333</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:46:01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.5921213275077106</v>
+      </c>
+      <c r="F61" t="n">
+        <v>94.27243392747388</v>
+      </c>
+      <c r="G61" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H61" t="n">
+        <v>54</v>
+      </c>
+      <c r="I61" t="n">
+        <v>80.5557</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1:20.56</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>76.7419</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="M61" t="n">
+        <v>3.647</v>
+      </c>
+      <c r="N61" t="n">
+        <v>4923.5463</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1:22:03.55</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>0,7,4,2,5,8,6,9,1,3</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>0:53;7:48;4:30;2:30;5:33;8:24;6:59;9:10;1:54;3:44</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>0:[0,1,2,5,7];7:[1,2,5,6];4:[3,5,7];2:[0,2,4];5:[0,5,7];8:[1,5];6:[0,4,5,6,7];9:[0];1:[2,4,5,6,7];3:[2,4,5,7]</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>c0:bw=53,experts=[0,1,2,5,7]; c7:bw=48,experts=[1,2,5,6]; c4:bw=30,experts=[3,5,7]; c2:bw=30,experts=[0,2,4]; c5:bw=33,experts=[0,5,7]; c8:bw=24,experts=[1,5]; c6:bw=59,experts=[0,4,5,6,7]; c9:bw=10,experts=[0]; c1:bw=54,experts=[2,4,5,6,7]; c3:bw=44,experts=[2,4,5,7]</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>5.3469,15.7006,8.9238,9.9821,2.9096,3.5202,11.3480,3.5559,13.8727,1.5821</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:47:21</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.5917733505460465</v>
+      </c>
+      <c r="F62" t="n">
+        <v>94.44529809465274</v>
+      </c>
+      <c r="G62" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H62" t="n">
+        <v>54</v>
+      </c>
+      <c r="I62" t="n">
+        <v>79.8807</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1:19.88</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>76.74039999999999</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2.9654</v>
+      </c>
+      <c r="N62" t="n">
+        <v>5003.4632</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1:23:23.46</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>5,6,2,9,1,3,8,4,7,0</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>5:49;6:37;2:29;9:38;1:33;3:43;8:55;4:38;7:43;0:60</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>5:[1,2,3,6];6:[3,5,6];2:[0,4];9:[0,4,7];1:[1,4,5];3:[0,1,2,7];8:[2,3,4,5,6];4:[3,4,6];7:[0,1,2,4];0:[0,1,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>c5:bw=49,experts=[1,2,3,6]; c6:bw=37,experts=[3,5,6]; c2:bw=29,experts=[0,4]; c9:bw=38,experts=[0,4,7]; c1:bw=33,experts=[1,4,5]; c3:bw=43,experts=[0,1,2,7]; c8:bw=55,experts=[2,3,4,5,6]; c4:bw=38,experts=[3,4,6]; c7:bw=43,experts=[0,1,2,4]; c0:bw=60,experts=[0,1,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2.9439,11.4423,9.5534,3.9506,14.0451,1.6526,3.6103,8.8255,15.6766,5.0402</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:48:40</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.5915605316973688</v>
+      </c>
+      <c r="F63" t="n">
+        <v>94.73724646588813</v>
+      </c>
+      <c r="G63" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H63" t="n">
+        <v>54</v>
+      </c>
+      <c r="I63" t="n">
+        <v>79.2565</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1:19.26</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>75.8501</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.1766</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3.2287</v>
+      </c>
+      <c r="N63" t="n">
+        <v>5082.7521</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1:24:42.75</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>8,6,9,4,5,0,3,2,1,7</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>8:13;6:62;9:16;4:60;5:67;0:28;3:53;2:42;1:75;7:44</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>8:[1];6:[0,2,3,4,6,7];9:[4];4:[0,2,4,5,6,7];5:[0,3,4,5,6,7];0:[4,6];3:[0,1,5,6,7];2:[1,4,5,7];1:[0,1,2,3,5,6,7];7:[4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>c8:bw=13,experts=[1]; c6:bw=62,experts=[0,2,3,4,6,7]; c9:bw=16,experts=[4]; c4:bw=60,experts=[0,2,4,5,6,7]; c5:bw=67,experts=[0,3,4,5,6,7]; c0:bw=28,experts=[4,6]; c3:bw=53,experts=[0,1,5,6,7]; c2:bw=42,experts=[1,4,5,7]; c1:bw=75,experts=[0,1,2,3,5,6,7]; c7:bw=44,experts=[4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>3.1526,11.7275,3.9311,9.3011,2.7332,5.1033,1.5966,10.0241,13.5321,14.7485</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:50:02</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.5919441186736908</v>
+      </c>
+      <c r="F64" t="n">
+        <v>94.2839582052858</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H64" t="n">
+        <v>54</v>
+      </c>
+      <c r="I64" t="n">
+        <v>82.04349999999999</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1:22.04</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>78.7496</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.1399</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3.153</v>
+      </c>
+      <c r="N64" t="n">
+        <v>5164.8335</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1:26:04.83</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>5,9,6,3,8,1,7,0,2,4</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>5:10;9:21;6:34;3:52;8:32;1:50;7:68;0:41;2:28;4:52</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>5:[0];9:[2,4];6:[1,3,5];3:[0,1,3,6,7];8:[0,2,3];1:[0,2,3,4,6];7:[0,2,3,4,6,7];0:[1,2,3,6];2:[1,2];4:[0,1,2,4,6]</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>c5:bw=10,experts=[0]; c9:bw=21,experts=[2,4]; c6:bw=34,experts=[1,3,5]; c3:bw=52,experts=[0,1,3,6,7]; c8:bw=32,experts=[0,2,3]; c1:bw=50,experts=[0,2,3,4,6]; c7:bw=68,experts=[0,2,3,4,6,7]; c0:bw=41,experts=[1,2,3,6]; c2:bw=28,experts=[1,2]; c4:bw=52,experts=[0,1,2,4,6]</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>3.6252,4.8295,11.5756,1.6047,3.3490,14.3367,15.2119,5.0487,10.2679,8.9005</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:51:23</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.5906738391972086</v>
+      </c>
+      <c r="F65" t="n">
+        <v>94.43761524277812</v>
+      </c>
+      <c r="G65" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H65" t="n">
+        <v>54</v>
+      </c>
+      <c r="I65" t="n">
+        <v>80.6362</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1:20.64</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>77.24809999999999</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.1708</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.2163</v>
+      </c>
+      <c r="N65" t="n">
+        <v>5245.5057</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>1:27:25.51</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>6,4,5,3,7,0,8,9,2,1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>6:50;4:38;5:24;3:38;7:34;0:32;8:53;9:59;2:56;1:28</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>6:[0,2,4,6,7];4:[3,4,7];5:[1,2];3:[1,3,6];7:[2,3,6];0:[1,5,6];8:[2,3,4,5,6];9:[0,1,4,5,6];2:[1,2,4,6,7];1:[3,7]</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>c6:bw=50,experts=[0,2,4,6,7]; c4:bw=38,experts=[3,4,7]; c5:bw=24,experts=[1,2]; c3:bw=38,experts=[1,3,6]; c7:bw=34,experts=[2,3,6]; c0:bw=32,experts=[1,5,6]; c8:bw=53,experts=[2,3,4,5,6]; c9:bw=59,experts=[0,1,4,5,6]; c2:bw=56,experts=[1,2,4,6,7]; c1:bw=28,experts=[3,7]</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>11.8801,9.4858,3.3364,1.7459,15.9480,5.1422,3.2129,3.7222,9.2555,13.5192</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:52:43</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.5876828101936342</v>
+      </c>
+      <c r="F66" t="n">
+        <v>94.87169637369392</v>
+      </c>
+      <c r="G66" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H66" t="n">
+        <v>54</v>
+      </c>
+      <c r="I66" t="n">
+        <v>80.3768</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>1:20.38</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>77.06910000000001</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.1566</v>
+      </c>
+      <c r="M66" t="n">
+        <v>3.1501</v>
+      </c>
+      <c r="N66" t="n">
+        <v>5325.9222</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1:28:45.92</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>7,5,4,6,8,3,0,2,1,9</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>7:10;5:29;4:57;6:50;8:66;3:42;0:41;2:28;1:58;9:47</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>7:[6];5:[4,6];4:[0,1,2,3,7];6:[0,1,4,5,6];8:[0,2,3,4,5,6];3:[3,4,5,7];0:[0,2,3,6];2:[4,7];1:[0,1,4,6,7];9:[0,1,4,5]</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>c7:bw=10,experts=[6]; c5:bw=29,experts=[4,6]; c4:bw=57,experts=[0,1,2,3,7]; c6:bw=50,experts=[0,1,4,5,6]; c8:bw=66,experts=[0,2,3,4,5,6]; c3:bw=42,experts=[3,4,5,7]; c0:bw=41,experts=[0,2,3,6]; c2:bw=28,experts=[4,7]; c1:bw=58,experts=[0,1,4,6,7]; c9:bw=47,experts=[0,1,4,5]</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>15.3763,3.1200,9.1417,12.1823,3.2637,1.4945,4.7668,9.8672,13.9641,3.8924</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:54:05</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.5880346998791078</v>
+      </c>
+      <c r="F67" t="n">
+        <v>94.79102642901044</v>
+      </c>
+      <c r="G67" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H67" t="n">
+        <v>54</v>
+      </c>
+      <c r="I67" t="n">
+        <v>81.82680000000001</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1:21.83</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>78.405</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.1646</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3.2528</v>
+      </c>
+      <c r="N67" t="n">
+        <v>5407.7869</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1:30:07.79</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2,5,1,8,9,6,4,0,3,7</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2:41;5:17;1:54;8:24;9:31;6:30;4:41;0:38;3:66;7:50</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2:[0,2,3,5];5:[0];1:[0,1,2,3,5];8:[1,3];9:[1,3,5];6:[1,2,6];4:[0,1,2,5];0:[0,4,7];3:[0,1,2,3,4,6];7:[1,2,4,5,6]</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>c2:bw=41,experts=[0,2,3,5]; c5:bw=17,experts=[0]; c1:bw=54,experts=[0,1,2,3,5]; c8:bw=24,experts=[1,3]; c9:bw=31,experts=[1,3,5]; c6:bw=30,experts=[1,2,6]; c4:bw=41,experts=[0,1,2,5]; c0:bw=38,experts=[0,4,7]; c3:bw=66,experts=[0,1,2,3,4,6]; c7:bw=50,experts=[1,2,4,5,6]</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>10.1346,2.9120,13.9913,2.9772,4.1906,12.4301,9.8635,4.7281,1.5458,15.6316</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:55:24</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.5856737368708026</v>
+      </c>
+      <c r="F68" t="n">
+        <v>94.22249539028887</v>
+      </c>
+      <c r="G68" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H68" t="n">
+        <v>54</v>
+      </c>
+      <c r="I68" t="n">
+        <v>79.4426</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1:19.44</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>75.8471</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="M68" t="n">
+        <v>3.4213</v>
+      </c>
+      <c r="N68" t="n">
+        <v>5487.2706</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1:31:27.27</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>4,5,1,3,6,0,2,9,7,8</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>4:51;5:48;1:36;3:25;6:53;0:32;2:43;9:60;7:59;8:10</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>4:[1,3,5,6,7];5:[2,3,5,6];1:[3,4,7];3:[0,6];6:[1,2,3,6,7];0:[0,1,5];2:[0,3,6,7];9:[0,1,2,3,4,7];7:[1,2,4,5,7];8:[5]</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>c4:bw=51,experts=[1,3,5,6,7]; c5:bw=48,experts=[2,3,5,6]; c1:bw=36,experts=[3,4,7]; c3:bw=25,experts=[0,6]; c6:bw=53,experts=[1,2,3,6,7]; c0:bw=32,experts=[0,1,5]; c2:bw=43,experts=[0,3,6,7]; c9:bw=60,experts=[0,1,2,3,4,7]; c7:bw=59,experts=[1,2,4,5,7]; c8:bw=10,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>8.9159,3.0239,13.7153,1.5427,11.3080,4.7720,9.7511,3.9580,15.7220,3.1382</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:56:46</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.5868240717967216</v>
+      </c>
+      <c r="F69" t="n">
+        <v>94.87169637369392</v>
+      </c>
+      <c r="G69" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H69" t="n">
+        <v>54</v>
+      </c>
+      <c r="I69" t="n">
+        <v>81.3137</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1:21.31</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>77.5198</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.1712</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3.6217</v>
+      </c>
+      <c r="N69" t="n">
+        <v>5568.6221</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1:32:48.62</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1,8,2,0,3,4,5,9,7,6</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1:42;8:31;2:58;0:30;3:26;4:49;5:45;9:15;7:28;6:32</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1:[3,5,6,7];8:[3,5,6];2:[0,1,3,4,5];0:[0,4,6];3:[4,7];4:[3,5,6,7];5:[1,2,5,6];9:[5];7:[0,2];6:[0,2,6]</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>c1:bw=42,experts=[3,5,6,7]; c8:bw=31,experts=[3,5,6]; c2:bw=58,experts=[0,1,3,4,5]; c0:bw=30,experts=[0,4,6]; c3:bw=26,experts=[4,7]; c4:bw=49,experts=[3,5,6,7]; c5:bw=45,experts=[1,2,5,6]; c9:bw=15,experts=[5]; c7:bw=28,experts=[0,2]; c6:bw=32,experts=[0,2,6]</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>14.1125,3.3172,9.9795,5.1008,1.6033,9.2073,2.9596,3.9151,15.4604,11.8640</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:58:06</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.5859860106136867</v>
+      </c>
+      <c r="F70" t="n">
+        <v>93.4119545175169</v>
+      </c>
+      <c r="G70" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H70" t="n">
+        <v>54</v>
+      </c>
+      <c r="I70" t="n">
+        <v>80.5116</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1:20.51</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>77.1135</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.1747</v>
+      </c>
+      <c r="M70" t="n">
+        <v>3.2224</v>
+      </c>
+      <c r="N70" t="n">
+        <v>5649.1726</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1:34:09.17</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>3,7,1,4,9,5,0,2,8,6</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>3:41;7:58;1:31;4:41;9:35;5:39;0:52;2:66;8:42;6:26</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>3:[0,2,4,7];7:[0,3,4,6,7];1:[4,6,7];4:[1,3,4,7];9:[1,2,3];5:[0,4,5];0:[0,1,3,5,6];2:[0,1,2,3,6,7];8:[0,2,3,6];6:[3,7]</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>c3:bw=41,experts=[0,2,4,7]; c7:bw=58,experts=[0,3,4,6,7]; c1:bw=31,experts=[4,6,7]; c4:bw=41,experts=[1,3,4,7]; c9:bw=35,experts=[1,2,3]; c5:bw=39,experts=[0,4,5]; c0:bw=52,experts=[0,1,3,5,6]; c2:bw=66,experts=[0,1,2,3,6,7]; c8:bw=42,experts=[0,2,3,6]; c6:bw=26,experts=[3,7]</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>1.6125,15.0991,14.3134,9.0793,3.5280,2.9147,5.5140,9.9466,3.3695,11.7364</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:59:27</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.5852045128949118</v>
+      </c>
+      <c r="F71" t="n">
+        <v>94.79102642901044</v>
+      </c>
+      <c r="G71" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H71" t="n">
+        <v>54</v>
+      </c>
+      <c r="I71" t="n">
+        <v>80.9191</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1:20.92</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>77.5423</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="M71" t="n">
+        <v>3.2094</v>
+      </c>
+      <c r="N71" t="n">
+        <v>5730.1359</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1:35:30.14</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1,9,7,3,0,6,2,4,5,8</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1:24;9:10;7:28;3:32;0:30;6:26;2:55;4:58;5:23;8:48</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1:[4,5];9:[0];7:[1,7];3:[1,4,7];0:[1,4,7];6:[2,5];2:[0,1,5,6,7];4:[0,1,2,4,6];5:[0,3];8:[2,4,5,7]</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>c1:bw=24,experts=[4,5]; c9:bw=10,experts=[0]; c7:bw=28,experts=[1,7]; c3:bw=32,experts=[1,4,7]; c0:bw=30,experts=[1,4,7]; c6:bw=26,experts=[2,5]; c2:bw=55,experts=[0,1,5,6,7]; c4:bw=58,experts=[0,1,2,4,6]; c5:bw=23,experts=[0,3]; c8:bw=48,experts=[2,4,5,7]</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>13.9880,3.8892,15.8535,1.6770,5.6344,11.7905,9.4042,9.0854,2.9007,3.3193</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:00:47</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.585453409063919</v>
+      </c>
+      <c r="F72" t="n">
+        <v>94.19176398279041</v>
+      </c>
+      <c r="G72" t="n">
+        <v>95.09834050399509</v>
+      </c>
+      <c r="H72" t="n">
+        <v>54</v>
+      </c>
+      <c r="I72" t="n">
+        <v>79.786</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1:19.79</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>76.31789999999999</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.1681</v>
+      </c>
+      <c r="M72" t="n">
+        <v>3.299</v>
+      </c>
+      <c r="N72" t="n">
+        <v>5809.961</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1:36:49.96</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>4,0,1,9,7,5,3,6,8,2</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>4:42;0:16;1:52;9:40;7:20;5:33;3:62;6:50;8:39;2:61</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>4:[3,4,5,7];0:[6];1:[0,1,3,5,6];9:[1,5,6,7];7:[1,7];5:[0,3,5];3:[0,1,2,3,5,7];6:[0,2,3,4,7];8:[2,4,5];2:[0,1,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>c4:bw=42,experts=[3,4,5,7]; c0:bw=16,experts=[6]; c1:bw=52,experts=[0,1,3,5,6]; c9:bw=40,experts=[1,5,6,7]; c7:bw=20,experts=[1,7]; c5:bw=33,experts=[0,3,5]; c3:bw=62,experts=[0,1,2,3,5,7]; c6:bw=50,experts=[0,2,3,4,7]; c8:bw=39,experts=[2,4,5]; c2:bw=61,experts=[0,1,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>8.6910,5.2172,14.0298,3.8970,15.2439,2.9000,1.5770,11.7512,3.3488,9.6620</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:02:08</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.5852596459760779</v>
+      </c>
+      <c r="F73" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="G73" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="H73" t="n">
+        <v>72</v>
+      </c>
+      <c r="I73" t="n">
+        <v>80.7787</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1:20.78</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>77.2535</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="M73" t="n">
+        <v>3.3484</v>
+      </c>
+      <c r="N73" t="n">
+        <v>5890.7835</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1:38:10.78</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>8,1,5,7,6,0,3,2,9,4</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>8:30;1:39;5:43;7:48;6:19;0:52;3:23;2:23;9:38;4:39</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>8:[2,3,5];1:[0,2,6];5:[0,2,5,7];7:[3,4,5,6];6:[2];0:[2,3,4,5,6];3:[3,6];2:[0,7];9:[3,5,6];4:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>c8:bw=30,experts=[2,3,5]; c1:bw=39,experts=[0,2,6]; c5:bw=43,experts=[0,2,5,7]; c7:bw=48,experts=[3,4,5,6]; c6:bw=19,experts=[2]; c0:bw=52,experts=[2,3,4,5,6]; c3:bw=23,experts=[3,6]; c2:bw=23,experts=[0,7]; c9:bw=38,experts=[3,5,6]; c4:bw=39,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>3.3832,13.7924,2.9920,15.4932,11.9239,5.0741,1.5170,9.9461,3.9289,9.2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:03:28</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.5854099369695038</v>
+      </c>
+      <c r="F74" t="n">
+        <v>95.109864781807</v>
+      </c>
+      <c r="G74" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="H74" t="n">
+        <v>72</v>
+      </c>
+      <c r="I74" t="n">
+        <v>79.62009999999999</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1:19.62</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>76.22190000000001</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.1723</v>
+      </c>
+      <c r="M74" t="n">
+        <v>3.225</v>
+      </c>
+      <c r="N74" t="n">
+        <v>5970.4428</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1:39:30.44</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2,8,3,1,5,9,0,7,6,4</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2:47;8:11;3:40;1:66;5:17;9:52;0:28;7:37;6:20;4:41</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>2:[0,4,6,7];8:[2];3:[1,2,3,4];1:[0,2,3,4,5,7];5:[0];9:[1,2,3,5,6];0:[1,7];7:[3,5,6];6:[5,7];4:[0,1,5,6]</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>c2:bw=47,experts=[0,4,6,7]; c8:bw=11,experts=[2]; c3:bw=40,experts=[1,2,3,4]; c1:bw=66,experts=[0,2,3,4,5,7]; c5:bw=17,experts=[0]; c9:bw=52,experts=[1,2,3,5,6]; c0:bw=28,experts=[1,7]; c7:bw=37,experts=[3,5,6]; c6:bw=20,experts=[5,7]; c4:bw=41,experts=[0,1,5,6]</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>9.2471,3.3820,1.6285,14.1221,2.9403,3.9715,4.8461,15.6944,11.8003,8.5896</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:04:48</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.585153197978274</v>
+      </c>
+      <c r="F75" t="n">
+        <v>93.83835279655808</v>
+      </c>
+      <c r="G75" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="H75" t="n">
+        <v>72</v>
+      </c>
+      <c r="I75" t="n">
+        <v>80.3747</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1:20.37</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>76.9226</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.2861</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6050.8558</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1:40:50.86</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>3,0,1,5,7,8,6,2,4,9</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>3:10;0:40;1:28;5:50;7:65;8:28;6:10;2:10;4:47;9:32</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>3:[6];0:[1,2,3,4];1:[3,4];5:[0,1,3,5,6];7:[1,2,3,5,6,7];8:[4,7];6:[2];2:[5];4:[0,2,3,7];9:[0,6,7]</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>c3:bw=10,experts=[6]; c0:bw=40,experts=[1,2,3,4]; c1:bw=28,experts=[3,4]; c5:bw=50,experts=[0,1,3,5,6]; c7:bw=65,experts=[1,2,3,5,6,7]; c8:bw=28,experts=[4,7]; c6:bw=10,experts=[2]; c2:bw=10,experts=[5]; c4:bw=47,experts=[0,2,3,7]; c9:bw=32,experts=[0,6,7]</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>1.6138,5.3704,13.9076,2.8406,15.9466,3.3766,11.1764,9.6280,9.1288,3.9338</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:06:09</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.5823804888298781</v>
+      </c>
+      <c r="F76" t="n">
+        <v>94.92931776275353</v>
+      </c>
+      <c r="G76" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="H76" t="n">
+        <v>72</v>
+      </c>
+      <c r="I76" t="n">
+        <v>80.6657</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1:20.67</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>77.1634</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.1751</v>
+      </c>
+      <c r="M76" t="n">
+        <v>3.3262</v>
+      </c>
+      <c r="N76" t="n">
+        <v>6131.5624</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1:42:11.56</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2,9,1,3,7,6,5,4,0,8</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2:40;9:61;1:54;3:20;7:28;6:56;5:31;4:56;0:60;8:53</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>2:[1,2,5,6];9:[0,2,4,5,6,7];1:[0,3,4,5,6];3:[5,6];7:[0,6];6:[0,3,4,5,7];5:[1,2,3];4:[1,2,3,4,6];0:[2,3,4,5,6,7];8:[1,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>c2:bw=40,experts=[1,2,5,6]; c9:bw=61,experts=[0,2,4,5,6,7]; c1:bw=54,experts=[0,3,4,5,6]; c3:bw=20,experts=[5,6]; c7:bw=28,experts=[0,6]; c6:bw=56,experts=[0,3,4,5,7]; c5:bw=31,experts=[1,2,3]; c4:bw=56,experts=[1,2,3,4,6]; c0:bw=60,experts=[2,3,4,5,6,7]; c8:bw=53,experts=[1,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>9.7111,3.9823,13.9883,1.5991,15.5287,11.9566,2.9301,8.8006,5.2829,3.3837</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:07:29</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.581931778419511</v>
+      </c>
+      <c r="F77" t="n">
+        <v>95.0061462814997</v>
+      </c>
+      <c r="G77" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="H77" t="n">
+        <v>72</v>
+      </c>
+      <c r="I77" t="n">
+        <v>79.9442</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1:19.94</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>76.8642</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.1717</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2.9074</v>
+      </c>
+      <c r="N77" t="n">
+        <v>6211.5471</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1:43:31.55</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>8,5,0,3,2,6,7,4,9,1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>8:29;5:37;0:31;3:15;2:25;6:23;7:66;4:60;9:57;1:53</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>8:[1,7];5:[4,6,7];0:[1,5,6];3:[6];2:[0,7];6:[5,6];7:[0,1,2,3,5,6];4:[1,2,4,5,6,7];9:[1,2,3,5,7];1:[0,2,3,4,5]</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>c8:bw=29,experts=[1,7]; c5:bw=37,experts=[4,6,7]; c0:bw=31,experts=[1,5,6]; c3:bw=15,experts=[6]; c2:bw=25,experts=[0,7]; c6:bw=23,experts=[5,6]; c7:bw=66,experts=[0,1,2,3,5,6]; c4:bw=60,experts=[1,2,4,5,6,7]; c9:bw=57,experts=[1,2,3,5,7]; c1:bw=53,experts=[0,2,3,4,5]</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>3.3845,2.9131,5.2548,1.5864,9.6411,11.4753,15.4184,9.1881,3.9199,14.0824</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:08:49</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.5817729306330713</v>
+      </c>
+      <c r="F78" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="G78" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="H78" t="n">
+        <v>72</v>
+      </c>
+      <c r="I78" t="n">
+        <v>80.3295</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1:20.33</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>76.5351</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.1643</v>
+      </c>
+      <c r="M78" t="n">
+        <v>3.6292</v>
+      </c>
+      <c r="N78" t="n">
+        <v>6291.9167</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1:44:51.92</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>9,2,1,8,4,7,6,0,3,5</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>9:29;2:34;1:62;8:10;4:10;7:10;6:57;0:63;3:40;5:59</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>9:[2,3];2:[3,5,6];1:[0,1,2,4,5,7];8:[2];4:[3];7:[1];6:[0,1,2,5,6];0:[0,1,2,3,6,7];3:[4,5,6,7];5:[0,1,2,4,5]</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>c9:bw=29,experts=[2,3]; c2:bw=34,experts=[3,5,6]; c1:bw=62,experts=[0,1,2,4,5,7]; c8:bw=10,experts=[2]; c4:bw=10,experts=[3]; c7:bw=10,experts=[1]; c6:bw=57,experts=[0,1,2,5,6]; c0:bw=63,experts=[0,1,2,3,6,7]; c3:bw=40,experts=[4,5,6,7]; c5:bw=59,experts=[0,1,2,4,5]</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>3.7327,9.8200,14.0197,3.4737,8.7731,16.0709,11.3106,4.9726,1.5272,2.8347</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:10:10</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.5808187716011703</v>
+      </c>
+      <c r="F79" t="n">
+        <v>94.52980946527352</v>
+      </c>
+      <c r="G79" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="H79" t="n">
+        <v>72</v>
+      </c>
+      <c r="I79" t="n">
+        <v>80.4425</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1:20.44</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>77.3764</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.1732</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2.8918</v>
+      </c>
+      <c r="N79" t="n">
+        <v>6372.4064</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1:46:12.41</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>0,4,3,7,8,1,9,6,5,2</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>0:26;4:23;3:38;7:36;8:54;1:41;9:31;6:57;5:63;2:34</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>0:[0,3];4:[2,3];3:[0,5,7];7:[1,4,7];8:[0,1,2,6,7];1:[1,4,5,7];9:[2,3,7];6:[0,2,3,4,7];5:[0,1,2,4,6,7];2:[4,6,7]</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>c0:bw=26,experts=[0,3]; c4:bw=23,experts=[2,3]; c3:bw=38,experts=[0,5,7]; c7:bw=36,experts=[1,4,7]; c8:bw=54,experts=[0,1,2,6,7]; c1:bw=41,experts=[1,4,5,7]; c9:bw=31,experts=[2,3,7]; c6:bw=57,experts=[0,2,3,4,7]; c5:bw=63,experts=[0,1,2,4,6,7]; c2:bw=34,experts=[4,6,7]</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>5.3796,9.5429,1.5893,15.2273,3.3818,14.2340,3.8653,11.5765,2.9173,9.6623</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:11:29</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.5812068342819561</v>
+      </c>
+      <c r="F80" t="n">
+        <v>94.77566072526122</v>
+      </c>
+      <c r="G80" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="H80" t="n">
+        <v>72</v>
+      </c>
+      <c r="I80" t="n">
+        <v>79.7247</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1:19.72</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>75.8477</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.1771</v>
+      </c>
+      <c r="M80" t="n">
+        <v>3.699</v>
+      </c>
+      <c r="N80" t="n">
+        <v>6452.1705</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1:47:32.17</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>6,9,0,4,7,8,5,3,1,2</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>6:21;9:10;0:36;4:80;7:46;8:44;5:53;3:26;1:37;2:33</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>6:[1,5];9:[4];0:[1,6,7];4:[0,1,2,3,4,5,6,7];7:[0,2,4,6];8:[0,4,6,7];5:[0,3,4,5,7];3:[0,4];1:[0,1,7];2:[2,3,5]</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>c6:bw=21,experts=[1,5]; c9:bw=10,experts=[4]; c0:bw=36,experts=[1,6,7]; c4:bw=80,experts=[0,1,2,3,4,5,6,7]; c7:bw=46,experts=[0,2,4,6]; c8:bw=44,experts=[0,4,6,7]; c5:bw=53,experts=[0,3,4,5,7]; c3:bw=26,experts=[0,4]; c1:bw=37,experts=[0,1,7]; c2:bw=33,experts=[2,3,5]</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>11.3751,3.8999,5.1318,8.8441,14.8668,3.3510,2.9584,1.5839,13.6254,10.2114</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:12:51</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.5816693598501437</v>
+      </c>
+      <c r="F81" t="n">
+        <v>94.37231100184388</v>
+      </c>
+      <c r="G81" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="H81" t="n">
+        <v>72</v>
+      </c>
+      <c r="I81" t="n">
+        <v>81.6229</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1:21.62</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>78.6113</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.1717</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2.8388</v>
+      </c>
+      <c r="N81" t="n">
+        <v>6533.8367</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1:48:53.84</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>5,9,7,1,3,4,2,0,6,8</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>5:65;9:53;7:48;1:31;3:31;4:57;2:44;0:47;6:39;8:51</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>5:[0,1,3,4,6,7];9:[0,1,3,4,6];7:[0,3,4,6];1:[4,5,7];3:[4,5,6];4:[0,2,4,6,7];2:[3,4,6,7];0:[0,2,6,7];6:[1,2,4];8:[0,1,2,3,5]</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>c5:bw=65,experts=[0,1,3,4,6,7]; c9:bw=53,experts=[0,1,3,4,6]; c7:bw=48,experts=[0,3,4,6]; c1:bw=31,experts=[4,5,7]; c3:bw=31,experts=[4,5,6]; c4:bw=57,experts=[0,2,4,6,7]; c2:bw=44,experts=[3,4,6,7]; c0:bw=47,experts=[0,2,6,7]; c6:bw=39,experts=[1,2,4]; c8:bw=51,experts=[0,1,2,3,5]</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>3.0678,3.9371,16.3055,14.1838,1.6881,9.1304,10.0557,5.3114,11.8473,3.0841</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:14:13</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.5801423164482143</v>
+      </c>
+      <c r="F82" t="n">
+        <v>94.7180393362016</v>
+      </c>
+      <c r="G82" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="H82" t="n">
+        <v>72</v>
+      </c>
+      <c r="I82" t="n">
+        <v>81.8693</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1:21.87</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>78.4151</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.1688</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3.2844</v>
+      </c>
+      <c r="N82" t="n">
+        <v>6615.7512</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1:50:15.75</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>6,2,3,1,4,5,9,7,8,0</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>6:51;2:45;3:67;1:49;4:42;5:30;9:26;7:58;8:48;0:50</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>6:[0,1,3,4,6];2:[2,3,4,5];3:[0,1,3,5,6,7];1:[0,2,6,7];4:[0,3,5,6];5:[3,4,7];9:[0,5];7:[1,2,4,5,7];8:[1,2,4,7];0:[0,1,2,4,5]</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>c6:bw=51,experts=[0,1,3,4,6]; c2:bw=45,experts=[2,3,4,5]; c3:bw=67,experts=[0,1,3,5,6,7]; c1:bw=49,experts=[0,2,6,7]; c4:bw=42,experts=[0,3,5,6]; c5:bw=30,experts=[3,4,7]; c9:bw=26,experts=[0,5]; c7:bw=58,experts=[1,2,4,5,7]; c8:bw=48,experts=[1,2,4,7]; c0:bw=50,experts=[0,1,2,4,5]</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>12.4495,10.1463,1.6099,13.9341,9.5253,2.8498,3.8898,15.1846,3.5118,5.3139</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:15:34</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.580579377286498</v>
+      </c>
+      <c r="F83" t="n">
+        <v>94.44913952059004</v>
+      </c>
+      <c r="G83" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="H83" t="n">
+        <v>72</v>
+      </c>
+      <c r="I83" t="n">
+        <v>80.5775</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1:20.58</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>77.1596</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.1715</v>
+      </c>
+      <c r="M83" t="n">
+        <v>3.2454</v>
+      </c>
+      <c r="N83" t="n">
+        <v>6696.3716</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1:51:36.37</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1,0,6,8,7,3,2,9,5,4</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1:64;0:30;6:36;8:58;7:40;3:39;2:30;9:56;5:40;4:30</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1:[0,2,3,5,6,7];0:[2,5,6];6:[0,4,7];8:[1,2,3,4,5];7:[1,2,5,7];3:[0,6,7];2:[3,5,7];9:[2,3,4,6,7];5:[1,3,4,6];4:[0,3,4]</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>c1:bw=64,experts=[0,2,3,5,6,7]; c0:bw=30,experts=[2,5,6]; c6:bw=36,experts=[0,4,7]; c8:bw=58,experts=[1,2,3,4,5]; c7:bw=40,experts=[1,2,5,7]; c3:bw=39,experts=[0,6,7]; c2:bw=30,experts=[3,5,7]; c9:bw=56,experts=[2,3,4,6,7]; c5:bw=40,experts=[1,3,4,6]; c4:bw=30,experts=[0,3,4]</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>13.4109,5.1999,11.8879,3.3771,15.6334,1.7047,10.2172,3.8970,2.9398,8.8917</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:16:56</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.5797557147386958</v>
+      </c>
+      <c r="F84" t="n">
+        <v>94.9139520590043</v>
+      </c>
+      <c r="G84" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="H84" t="n">
+        <v>72</v>
+      </c>
+      <c r="I84" t="n">
+        <v>82.1947</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1:22.19</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>78.68170000000001</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.1695</v>
+      </c>
+      <c r="M84" t="n">
+        <v>3.3426</v>
+      </c>
+      <c r="N84" t="n">
+        <v>6778.609</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1:52:58.61</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>9,4,2,7,5,0,6,1,8,3</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>9:51;4:10;2:41;7:37;5:10;0:10;6:53;1:63;8:39;3:42</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>9:[0,2,4,5,6];4:[2];2:[2,3,4,7];7:[0,1,4];5:[2];0:[6];6:[2,3,5,6,7];1:[0,1,3,5,6,7];8:[0,4,6];3:[0,1,3,7]</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>c9:bw=51,experts=[0,2,4,5,6]; c4:bw=10,experts=[2]; c2:bw=41,experts=[2,3,4,7]; c7:bw=37,experts=[0,1,4]; c5:bw=10,experts=[2]; c0:bw=10,experts=[6]; c6:bw=53,experts=[2,3,5,6,7]; c1:bw=63,experts=[0,1,3,5,6,7]; c8:bw=39,experts=[0,4,6]; c3:bw=42,experts=[0,1,3,7]</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>4.0048,9.3440,10.7978,15.6597,2.9234,5.2398,12.0333,13.6853,3.3921,1.6015</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:18:16</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.5788843710246214</v>
+      </c>
+      <c r="F85" t="n">
+        <v>94.24554394591273</v>
+      </c>
+      <c r="G85" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="H85" t="n">
+        <v>72</v>
+      </c>
+      <c r="I85" t="n">
+        <v>80.2257</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1:20.23</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>76.80370000000001</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.1699</v>
+      </c>
+      <c r="M85" t="n">
+        <v>3.2511</v>
+      </c>
+      <c r="N85" t="n">
+        <v>6858.8827</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1:54:18.88</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>8,3,1,6,9,2,7,5,4,0</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>8:67;3:32;1:58;6:10;9:20;2:36;7:47;5:20;4:27;0:10</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>8:[1,2,3,4,5,7];3:[4,5,6];1:[1,2,5,6,7];6:[4];9:[1,7];2:[0,1,6];7:[0,1,2,4];5:[0,6];4:[1,3];0:[0]</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>c8:bw=67,experts=[1,2,3,4,5,7]; c3:bw=32,experts=[4,5,6]; c1:bw=58,experts=[1,2,5,6,7]; c6:bw=10,experts=[4]; c9:bw=20,experts=[1,7]; c2:bw=36,experts=[0,1,6]; c7:bw=47,experts=[0,1,2,4]; c5:bw=20,experts=[0,6]; c4:bw=27,experts=[1,3]; c0:bw=10,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>3.3763,1.5809,13.8987,11.8069,3.8488,9.7051,16.1144,2.9233,8.6021,4.9471</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:19:38</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.57834084984345</v>
+      </c>
+      <c r="F86" t="n">
+        <v>95.24815611555009</v>
+      </c>
+      <c r="G86" t="n">
+        <v>95.24815611555009</v>
+      </c>
+      <c r="H86" t="n">
+        <v>85</v>
+      </c>
+      <c r="I86" t="n">
+        <v>82.1497</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1:22.15</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>78.7837</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="M86" t="n">
+        <v>3.1874</v>
+      </c>
+      <c r="N86" t="n">
+        <v>6941.192</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1:55:41.19</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>0,2,8,6,1,4,9,3,5,7</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>0:38;2:45;8:70;6:42;1:57;4:42;9:58;3:51;5:12;7:11</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>0:[1,3,4];2:[1,2,6,7];8:[0,1,2,4,5,6,7];6:[0,2,5,6];1:[0,1,2,4,5];4:[0,2,4,7];9:[2,3,4,6,7];3:[0,1,2,3,4];5:[1];7:[4]</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>c0:bw=38,experts=[1,3,4]; c2:bw=45,experts=[1,2,6,7]; c8:bw=70,experts=[0,1,2,4,5,6,7]; c6:bw=42,experts=[0,2,5,6]; c1:bw=57,experts=[0,1,2,4,5]; c4:bw=42,experts=[0,2,4,7]; c9:bw=58,experts=[2,3,4,6,7]; c3:bw=51,experts=[0,1,2,3,4]; c5:bw=12,experts=[1]; c7:bw=11,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>5.3087,10.1282,3.3921,11.6245,14.6346,9.3576,3.6808,1.5818,3.0701,16.0054</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:21:01</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.5794584657096248</v>
+      </c>
+      <c r="F87" t="n">
+        <v>94.75645359557468</v>
+      </c>
+      <c r="G87" t="n">
+        <v>95.24815611555009</v>
+      </c>
+      <c r="H87" t="n">
+        <v>85</v>
+      </c>
+      <c r="I87" t="n">
+        <v>82.6253</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>1:22.63</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>79.2372</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="M87" t="n">
+        <v>3.2204</v>
+      </c>
+      <c r="N87" t="n">
+        <v>7023.8609</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1:57:03.86</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>5,8,2,6,0,4,7,3,1,9</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>5:47;8:28;2:24;6:55;0:30;4:18;7:44;3:28;1:72;9:43</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>5:[1,2,4,7];8:[1,7];2:[4,5];6:[1,2,4,5,6];0:[1,2,7];4:[4];7:[0,2,3,5];3:[0,3];1:[0,1,2,3,4,5,7];9:[0,2,5,7]</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>c5:bw=47,experts=[1,2,4,7]; c8:bw=28,experts=[1,7]; c2:bw=24,experts=[4,5]; c6:bw=55,experts=[1,2,4,5,6]; c0:bw=30,experts=[1,2,7]; c4:bw=18,experts=[4]; c7:bw=44,experts=[0,2,3,5]; c3:bw=28,experts=[0,3]; c1:bw=72,experts=[0,1,2,3,4,5,7]; c9:bw=43,experts=[0,2,5,7]</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>2.7896,3.0360,10.0381,12.0213,5.7088,9.4864,17.0318,1.6205,13.5845,3.9201</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:22:22</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.5771131186504014</v>
+      </c>
+      <c r="F88" t="n">
+        <v>95.21358328211431</v>
+      </c>
+      <c r="G88" t="n">
+        <v>95.24815611555009</v>
+      </c>
+      <c r="H88" t="n">
+        <v>85</v>
+      </c>
+      <c r="I88" t="n">
+        <v>80.6168</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>1:20.62</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>77.5454</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.1568</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2.9138</v>
+      </c>
+      <c r="N88" t="n">
+        <v>7104.5229</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1:58:24.52</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1,2,7,5,6,3,4,9,8,0</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1:29;2:67;7:22;5:10;6:60;3:68;4:34;9:37;8:46;0:35</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1:[2,3];2:[0,3,4,5,6,7];7:[1,6];5:[7];6:[0,1,2,5,6,7];3:[0,1,3,4,6,7];4:[3,5,6];9:[0,2,7];8:[0,4,6,7];0:[1,2,3]</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>c1:bw=29,experts=[2,3]; c2:bw=67,experts=[0,3,4,5,6,7]; c7:bw=22,experts=[1,6]; c5:bw=10,experts=[7]; c6:bw=60,experts=[0,1,2,5,6,7]; c3:bw=68,experts=[0,1,3,4,6,7]; c4:bw=34,experts=[3,5,6]; c9:bw=37,experts=[0,2,7]; c8:bw=46,experts=[0,4,6,7]; c0:bw=35,experts=[1,2,3]</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>14.0589,9.3517,15.4352,2.9574,11.8763,1.6044,9.1087,4.5091,3.5790,5.0646</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:23:43</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.5763488485238076</v>
+      </c>
+      <c r="F89" t="n">
+        <v>94.39151813153042</v>
+      </c>
+      <c r="G89" t="n">
+        <v>95.24815611555009</v>
+      </c>
+      <c r="H89" t="n">
+        <v>85</v>
+      </c>
+      <c r="I89" t="n">
+        <v>81.6123</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>1:21.61</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>78.0624</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="M89" t="n">
+        <v>3.3799</v>
+      </c>
+      <c r="N89" t="n">
+        <v>7186.1795</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1:59:46.18</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>8,6,3,7,0,4,9,1,5,2</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>8:43;6:27;3:33;7:41;0:62;4:38;9:31;1:28;5:30;2:46</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>8:[0,1,6,7];6:[1,7];3:[2,5,6];7:[0,1,6,7];0:[0,2,3,4,6,7];4:[2,4,5];9:[0,2,5];1:[1,4];5:[1,2,5];2:[0,1,4,5]</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>c8:bw=43,experts=[0,1,6,7]; c6:bw=27,experts=[1,7]; c3:bw=33,experts=[2,5,6]; c7:bw=41,experts=[0,1,6,7]; c0:bw=62,experts=[0,2,3,4,6,7]; c4:bw=38,experts=[2,4,5]; c9:bw=31,experts=[0,2,5]; c1:bw=28,experts=[1,4]; c5:bw=30,experts=[1,2,5]; c2:bw=46,experts=[0,1,4,5]</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>3.2970,11.8098,1.5988,15.8242,5.4969,9.1643,3.9073,13.4068,3.0398,10.5175</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:25:04</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.5787238885057547</v>
+      </c>
+      <c r="F90" t="n">
+        <v>94.87169637369392</v>
+      </c>
+      <c r="G90" t="n">
+        <v>95.24815611555009</v>
+      </c>
+      <c r="H90" t="n">
+        <v>85</v>
+      </c>
+      <c r="I90" t="n">
+        <v>80.7341</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>1:20.73</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>77.2452</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="M90" t="n">
+        <v>3.3228</v>
+      </c>
+      <c r="N90" t="n">
+        <v>7266.9612</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>2:01:06.96</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>3,8,2,9,7,5,0,6,4,1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>3:31;8:74;2:44;9:60;7:21;5:46;0:13;6:32;4:30;1:41</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>3:[3,5,6];8:[0,1,2,3,4,5,7];2:[4,5,6,7];9:[0,1,3,4,5,6];7:[4,6];5:[0,3,5,6];0:[0];6:[0,2,6];4:[0,2,7];1:[1,3,5,7]</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>c3:bw=31,experts=[3,5,6]; c8:bw=74,experts=[0,1,2,3,4,5,7]; c2:bw=44,experts=[4,5,6,7]; c9:bw=60,experts=[0,1,3,4,5,6]; c7:bw=21,experts=[4,6]; c5:bw=46,experts=[0,3,5,6]; c0:bw=13,experts=[0]; c6:bw=32,experts=[0,2,6]; c4:bw=30,experts=[0,2,7]; c1:bw=41,experts=[1,3,5,7]</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>1.5823,3.3264,9.8306,4.1104,16.2705,3.0608,5.3541,11.0222,9.2422,13.4457</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:26:25</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.5770871664507389</v>
+      </c>
+      <c r="F91" t="n">
+        <v>94.22249539028887</v>
+      </c>
+      <c r="G91" t="n">
+        <v>95.24815611555009</v>
+      </c>
+      <c r="H91" t="n">
+        <v>85</v>
+      </c>
+      <c r="I91" t="n">
+        <v>80.4654</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>1:20.47</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>76.9278</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.1714</v>
+      </c>
+      <c r="M91" t="n">
+        <v>3.3652</v>
+      </c>
+      <c r="N91" t="n">
+        <v>7347.472</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>2:02:27.47</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>7,1,3,9,0,6,2,5,8,4</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>7:72;1:31;3:36;9:63;0:64;6:26;2:21;5:27;8:50;4:35</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>7:[0,1,2,3,4,5,6];1:[2,4,7];3:[0,1,2];9:[0,2,3,5,6,7];0:[0,2,3,4,5,6];6:[4,5];2:[1,3];5:[1,7];8:[0,3,4,6,7];4:[2,4,6]</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>c7:bw=72,experts=[0,1,2,3,4,5,6]; c1:bw=31,experts=[2,4,7]; c3:bw=36,experts=[0,1,2]; c9:bw=63,experts=[0,2,3,5,6,7]; c0:bw=64,experts=[0,2,3,4,5,6]; c6:bw=26,experts=[4,5]; c2:bw=21,experts=[1,3]; c5:bw=27,experts=[1,7]; c8:bw=50,experts=[0,3,4,6,7]; c4:bw=35,experts=[2,4,6]</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>15.8386,13.7296,1.6033,3.9180,5.0853,11.7342,9.5655,2.7786,3.3342,9.3405</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:27:45</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.5755084164588695</v>
+      </c>
+      <c r="F92" t="n">
+        <v>94.91779348494161</v>
+      </c>
+      <c r="G92" t="n">
+        <v>95.24815611555009</v>
+      </c>
+      <c r="H92" t="n">
+        <v>85</v>
+      </c>
+      <c r="I92" t="n">
+        <v>79.91240000000001</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1:19.91</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>76.4109</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.1747</v>
+      </c>
+      <c r="M92" t="n">
+        <v>3.3257</v>
+      </c>
+      <c r="N92" t="n">
+        <v>7427.4316</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>2:03:47.43</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1,9,5,7,3,4,0,6,2,8</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1:50;9:35;5:52;7:51;3:40;4:54;0:22;6:29;2:11;8:23</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1:[2,3,4,6,7];9:[1,5,7];5:[1,2,3,4,5];7:[0,1,4,5,6];3:[2,3,6,7];4:[1,2,5,6,7];0:[0,7];6:[3,6];2:[0];8:[5,6]</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>c1:bw=50,experts=[2,3,4,6,7]; c9:bw=35,experts=[1,5,7]; c5:bw=52,experts=[1,2,3,4,5]; c7:bw=51,experts=[0,1,4,5,6]; c3:bw=40,experts=[2,3,6,7]; c4:bw=54,experts=[1,2,5,6,7]; c0:bw=22,experts=[0,7]; c6:bw=29,experts=[3,6]; c2:bw=11,experts=[0]; c8:bw=23,experts=[5,6]</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>13.7823,3.9846,2.9625,15.4525,1.5284,8.7072,5.2552,11.8955,9.7541,3.0887</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:29:06</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.5754602297102398</v>
+      </c>
+      <c r="F93" t="n">
+        <v>94.94084204056546</v>
+      </c>
+      <c r="G93" t="n">
+        <v>95.24815611555009</v>
+      </c>
+      <c r="H93" t="n">
+        <v>85</v>
+      </c>
+      <c r="I93" t="n">
+        <v>80.8908</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>1:20.89</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>77.5682</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.1698</v>
+      </c>
+      <c r="M93" t="n">
+        <v>3.1519</v>
+      </c>
+      <c r="N93" t="n">
+        <v>7508.37</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>2:05:08.37</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>3,7,1,0,8,6,9,2,5,4</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>3:28;7:34;1:20;0:29;8:19;6:45;9:56;2:25;5:66;4:26</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>3:[1,2];7:[2,4,6];1:[5,6];0:[4,7];8:[4];6:[2,3,6,7];9:[2,3,4,6,7];2:[0,5];5:[0,1,2,3,4,7];4:[0,1]</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>c3:bw=28,experts=[1,2]; c7:bw=34,experts=[2,4,6]; c1:bw=20,experts=[5,6]; c0:bw=29,experts=[4,7]; c8:bw=19,experts=[4]; c6:bw=45,experts=[2,3,6,7]; c9:bw=56,experts=[2,3,4,6,7]; c2:bw=25,experts=[0,5]; c5:bw=66,experts=[0,1,2,3,4,7]; c4:bw=26,experts=[0,1]</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>1.6110,15.6569,13.7089,5.2726,3.5800,12.6226,3.5507,9.4981,2.9197,9.1476</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:30:25</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.5747258695115656</v>
+      </c>
+      <c r="F94" t="n">
+        <v>90.35802089735709</v>
+      </c>
+      <c r="G94" t="n">
+        <v>95.24815611555009</v>
+      </c>
+      <c r="H94" t="n">
+        <v>85</v>
+      </c>
+      <c r="I94" t="n">
+        <v>79.4517</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>1:19.45</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>76.14230000000001</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.1683</v>
+      </c>
+      <c r="M94" t="n">
+        <v>3.1402</v>
+      </c>
+      <c r="N94" t="n">
+        <v>7587.8682</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>2:06:27.87</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1,3,7,9,6,8,5,4,0,2</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1:47;3:31;7:22;9:58;6:22;8:10;5:10;4:32;0:19;2:51</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1:[1,2,5,6];3:[0,2,5];7:[2,5];9:[1,2,3,4,6];6:[2,5];8:[6];5:[6];4:[1,2,4];0:[7];2:[3,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>c1:bw=47,experts=[1,2,5,6]; c3:bw=31,experts=[0,2,5]; c7:bw=22,experts=[2,5]; c9:bw=58,experts=[1,2,3,4,6]; c6:bw=22,experts=[2,5]; c8:bw=10,experts=[6]; c5:bw=10,experts=[6]; c4:bw=32,experts=[1,2,4]; c0:bw=19,experts=[7]; c2:bw=51,experts=[3,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>13.3521,1.6045,15.6687,3.9456,11.4656,3.3517,2.8462,9.1046,5.3169,9.4863</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:31:47</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.5744071953131075</v>
+      </c>
+      <c r="F95" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="G95" t="n">
+        <v>95.24815611555009</v>
+      </c>
+      <c r="H95" t="n">
+        <v>85</v>
+      </c>
+      <c r="I95" t="n">
+        <v>81.9415</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>1:21.94</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>78.2127</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.1753</v>
+      </c>
+      <c r="M95" t="n">
+        <v>3.5524</v>
+      </c>
+      <c r="N95" t="n">
+        <v>7669.8557</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>2:07:49.86</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>7,2,5,4,6,9,1,8,0,3</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>7:45;2:65;5:41;4:31;6:30;9:50;1:70;8:10;0:55;3:34</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>7:[1,2,3,5];2:[0,2,3,4,5,6];5:[0,1,3,5];4:[0,2,7];6:[0,1,4];9:[0,1,2,3,4];1:[0,1,2,3,4,5,7];8:[1];0:[0,1,5,6,7];3:[2,4,6]</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>c7:bw=45,experts=[1,2,3,5]; c2:bw=65,experts=[0,2,3,4,5,6]; c5:bw=41,experts=[0,1,3,5]; c4:bw=31,experts=[0,2,7]; c6:bw=30,experts=[0,1,4]; c9:bw=50,experts=[0,1,2,3,4]; c1:bw=70,experts=[0,1,2,3,4,5,7]; c8:bw=10,experts=[1]; c0:bw=55,experts=[0,1,5,6,7]; c3:bw=34,experts=[2,4,6]</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>16.0515,10.1601,2.9396,9.2508,11.9090,3.9824,13.6413,3.3584,5.3047,1.6148</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:33:07</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.574891139908711</v>
+      </c>
+      <c r="F96" t="n">
+        <v>94.78334357713584</v>
+      </c>
+      <c r="G96" t="n">
+        <v>95.24815611555009</v>
+      </c>
+      <c r="H96" t="n">
+        <v>85</v>
+      </c>
+      <c r="I96" t="n">
+        <v>80.3206</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>1:20.32</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>76.8115</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="M96" t="n">
+        <v>3.3422</v>
+      </c>
+      <c r="N96" t="n">
+        <v>7750.2266</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>2:09:10.23</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>7,9,4,6,0,3,1,8,2,5</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>7:59;9:42;4:15;6:40;0:35;3:41;1:31;8:76;2:23;5:10</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>7:[1,2,3,4,5];9:[1,3,4,7];4:[4];6:[0,1,3,7];0:[1,3,5];3:[0,1,2,3];1:[2,4,6];8:[0,1,2,3,4,5,6];2:[3,6];5:[5]</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>c7:bw=59,experts=[1,2,3,4,5]; c9:bw=42,experts=[1,3,4,7]; c4:bw=15,experts=[4]; c6:bw=40,experts=[0,1,3,7]; c0:bw=35,experts=[1,3,5]; c3:bw=41,experts=[0,1,2,3]; c1:bw=31,experts=[2,4,6]; c8:bw=76,experts=[0,1,2,3,4,5,6]; c2:bw=23,experts=[3,6]; c5:bw=10,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>15.9414,3.8972,9.2399,11.3281,5.0588,1.5493,13.9056,3.4070,9.5793,2.9050</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:34:28</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.5753224524627862</v>
+      </c>
+      <c r="F97" t="n">
+        <v>95.72065150583897</v>
+      </c>
+      <c r="G97" t="n">
+        <v>95.72065150583897</v>
+      </c>
+      <c r="H97" t="n">
+        <v>96</v>
+      </c>
+      <c r="I97" t="n">
+        <v>80.6875</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>1:20.69</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>77.1943</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="M97" t="n">
+        <v>3.3101</v>
+      </c>
+      <c r="N97" t="n">
+        <v>7830.9633</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>2:10:30.96</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2,9,3,1,5,4,6,7,0,8</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2:65;9:44;3:46;1:36;5:60;4:49;6:31;7:50;0:36;8:64</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>2:[1,2,4,5,6,7];9:[1,3,4,6];3:[1,2,3,5];1:[0,2,5];5:[2,3,4,5,6,7];4:[1,4,6,7];6:[1,5,7];7:[2,3,4,5,7];0:[2,4,7];8:[1,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>c2:bw=65,experts=[1,2,4,5,6,7]; c9:bw=44,experts=[1,3,4,6]; c3:bw=46,experts=[1,2,3,5]; c1:bw=36,experts=[0,2,5]; c5:bw=60,experts=[2,3,4,5,6,7]; c4:bw=49,experts=[1,4,6,7]; c6:bw=31,experts=[1,5,7]; c7:bw=50,experts=[2,3,4,5,7]; c0:bw=36,experts=[2,4,7]; c8:bw=64,experts=[1,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>10.1890,4.1733,1.8636,13.3858,3.1318,9.2274,11.1199,15.4528,5.3064,3.3442</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:35:50</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.5748564651990729</v>
+      </c>
+      <c r="F98" t="n">
+        <v>94.56438229870928</v>
+      </c>
+      <c r="G98" t="n">
+        <v>95.72065150583897</v>
+      </c>
+      <c r="H98" t="n">
+        <v>96</v>
+      </c>
+      <c r="I98" t="n">
+        <v>81.6331</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>1:21.63</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>78.1956</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="M98" t="n">
+        <v>3.2637</v>
+      </c>
+      <c r="N98" t="n">
+        <v>7912.6458</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>2:11:52.65</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>0,9,8,4,7,1,3,5,6,2</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>0:41;9:43;8:43;4:16;7:30;1:50;3:35;5:46;6:50;2:54</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>0:[0,3,4,5];9:[0,2,4,5];8:[1,4,5,7];4:[2];7:[0,4,5];1:[2,3,4,5,6];3:[1,2,5];5:[0,2,4,6];6:[1,2,5,6,7];2:[1,2,4,6,7]</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>c0:bw=41,experts=[0,3,4,5]; c9:bw=43,experts=[0,2,4,5]; c8:bw=43,experts=[1,4,5,7]; c4:bw=16,experts=[2]; c7:bw=30,experts=[0,4,5]; c1:bw=50,experts=[2,3,4,5,6]; c3:bw=35,experts=[1,2,5]; c5:bw=46,experts=[0,2,4,6]; c6:bw=50,experts=[1,2,5,6,7]; c2:bw=54,experts=[1,2,4,6,7]</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>5.2879,3.5125,3.3488,9.5597,15.9422,13.8463,1.7122,3.1870,11.9784,9.8206</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:37:13</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.572934262124744</v>
+      </c>
+      <c r="F99" t="n">
+        <v>95.28657037492317</v>
+      </c>
+      <c r="G99" t="n">
+        <v>95.72065150583897</v>
+      </c>
+      <c r="H99" t="n">
+        <v>96</v>
+      </c>
+      <c r="I99" t="n">
+        <v>82.887</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>1:22.89</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>79.6142</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.1795</v>
+      </c>
+      <c r="M99" t="n">
+        <v>3.0924</v>
+      </c>
+      <c r="N99" t="n">
+        <v>7995.5837</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>2:13:15.58</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>4,8,9,7,6,5,0,3,1,2</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>4:52;8:54;9:27;7:24;6:36;5:49;0:33;3:25;1:26;2:24</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>4:[0,1,3,4,7];8:[0,4,5,6,7];9:[0,2];7:[1,6];6:[1,2,3];5:[0,3,5,7];0:[0,1,5];3:[4,6];1:[0,4];2:[1,3]</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>c4:bw=52,experts=[0,1,3,4,7]; c8:bw=54,experts=[0,4,5,6,7]; c9:bw=27,experts=[0,2]; c7:bw=24,experts=[1,6]; c6:bw=36,experts=[1,2,3]; c5:bw=49,experts=[0,3,5,7]; c0:bw=33,experts=[0,1,5]; c3:bw=25,experts=[4,6]; c1:bw=26,experts=[0,4]; c2:bw=24,experts=[1,3]</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>9.1984,3.3894,3.9335,16.1891,12.7093,2.9991,5.3284,1.5907,13.8637,10.4125</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:38:35</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.5711877715856511</v>
+      </c>
+      <c r="F100" t="n">
+        <v>94.89474492931777</v>
+      </c>
+      <c r="G100" t="n">
+        <v>95.72065150583897</v>
+      </c>
+      <c r="H100" t="n">
+        <v>96</v>
+      </c>
+      <c r="I100" t="n">
+        <v>82.24850000000001</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>1:22.25</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>78.7923</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.1678</v>
+      </c>
+      <c r="M100" t="n">
+        <v>3.2874</v>
+      </c>
+      <c r="N100" t="n">
+        <v>8077.8736</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>2:14:37.87</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>8,5,7,1,3,9,4,0,2,6</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>8:34;5:49;7:45;1:59;3:38;9:20;4:24;0:40;2:31;6:35</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>8:[2,6,7];5:[1,2,5,6];7:[0,3,4,5];1:[0,3,4,6,7];3:[0,4,5];9:[1,2];4:[0,1];0:[1,2,3,5];2:[0,4,6];6:[1,4,5]</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>c8:bw=34,experts=[2,6,7]; c5:bw=49,experts=[1,2,5,6]; c7:bw=45,experts=[0,3,4,5]; c1:bw=59,experts=[0,3,4,6,7]; c3:bw=38,experts=[0,4,5]; c9:bw=20,experts=[1,2]; c4:bw=24,experts=[0,1]; c0:bw=40,experts=[1,2,3,5]; c2:bw=31,experts=[0,4,6]; c6:bw=35,experts=[1,4,5]</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>3.5429,3.4236,15.9938,13.7560,1.5999,4.0289,9.1864,5.2983,9.6735,12.2891</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:39:55</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.5724017654758632</v>
+      </c>
+      <c r="F101" t="n">
+        <v>95.06376767055932</v>
+      </c>
+      <c r="G101" t="n">
+        <v>95.72065150583897</v>
+      </c>
+      <c r="H101" t="n">
+        <v>96</v>
+      </c>
+      <c r="I101" t="n">
+        <v>80.0741</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>1:20.07</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>77.0308</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="M101" t="n">
+        <v>2.8749</v>
+      </c>
+      <c r="N101" t="n">
+        <v>8157.9978</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>2:15:58.00</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2,8,9,5,6,1,4,7,3,0</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>2:30;8:44;9:53;5:18;6:44;1:17;4:65;7:10;3:42;0:64</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>2:[0,2,4];8:[0,1,2,4];9:[0,1,3,5,6];5:[7];6:[1,3,4,5];1:[6];4:[0,1,4,5,6,7];7:[7];3:[3,4,6,7];0:[0,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>c2:bw=30,experts=[0,2,4]; c8:bw=44,experts=[0,1,2,4]; c9:bw=53,experts=[0,1,3,5,6]; c5:bw=18,experts=[7]; c6:bw=44,experts=[1,3,4,5]; c1:bw=17,experts=[6]; c4:bw=65,experts=[0,1,4,5,6,7]; c7:bw=10,experts=[7]; c3:bw=42,experts=[3,4,6,7]; c0:bw=64,experts=[0,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>10.1887,2.9707,3.9232,2.9304,11.7980,13.6253,8.8498,15.8953,1.5823,5.2671</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
